--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.021182</v>
+        <v>0.021256</v>
       </c>
       <c r="F3" t="n">
         <v>0.05166</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.021182</v>
+        <v>0.021256</v>
       </c>
       <c r="F4" t="n">
         <v>0.05166</v>
@@ -1128,7 +1128,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003062</v>
+        <v>0.002988</v>
       </c>
       <c r="F32" t="n">
         <v>-0.000124</v>
@@ -1150,7 +1150,7 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003062</v>
+        <v>0.002988</v>
       </c>
       <c r="F33" t="n">
         <v>-0.000124</v>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.021256</v>
+        <v>0.021339</v>
       </c>
       <c r="F3" t="n">
         <v>0.05166</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.021256</v>
+        <v>0.021339</v>
       </c>
       <c r="F4" t="n">
         <v>0.05166</v>
@@ -647,7 +647,7 @@
         <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1253</v>
+        <v>5.0856</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1247</v>
+        <v>5.085</v>
       </c>
     </row>
     <row r="12">
@@ -836,16 +836,16 @@
         <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
         <v>368886</v>
       </c>
       <c r="F19" t="n">
-        <v>369742</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="20">
@@ -911,7 +911,7 @@
         <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.086537</v>
+        <v>-1.85271</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.086663</v>
+        <v>-1.852924</v>
       </c>
     </row>
     <row r="24">
@@ -1012,16 +1012,16 @@
         <v>44500</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
         <v>-0.259972</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5941920000000001</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="28">
@@ -1128,7 +1128,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.002988</v>
+        <v>0.002905</v>
       </c>
       <c r="F32" t="n">
         <v>-0.000124</v>
@@ -1150,7 +1150,7 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002988</v>
+        <v>0.002905</v>
       </c>
       <c r="F33" t="n">
         <v>-0.000124</v>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.021339</v>
+        <v>0.021433</v>
       </c>
       <c r="F3" t="n">
         <v>0.05166</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.021339</v>
+        <v>0.021433</v>
       </c>
       <c r="F4" t="n">
         <v>0.05166</v>
@@ -647,7 +647,7 @@
         <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0856</v>
+        <v>5.0979</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>5.085</v>
+        <v>5.0973</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.85271</v>
+        <v>-1.615331</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.852924</v>
+        <v>-1.615518</v>
       </c>
     </row>
     <row r="24">
@@ -1128,7 +1128,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.002905</v>
+        <v>0.002811</v>
       </c>
       <c r="F32" t="n">
         <v>-0.000124</v>
@@ -1150,7 +1150,7 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002905</v>
+        <v>0.002811</v>
       </c>
       <c r="F33" t="n">
         <v>-0.000124</v>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.021433</v>
+        <v>0.02154</v>
       </c>
       <c r="F3" t="n">
         <v>0.05166</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.021433</v>
+        <v>0.02154</v>
       </c>
       <c r="F4" t="n">
         <v>0.05166</v>
@@ -528,16 +528,16 @@
         <v>44469</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
         <v>1.16</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="6">
@@ -572,16 +572,16 @@
         <v>44469</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
         <v>1.2</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.01</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0979</v>
+        <v>5.1149</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0973</v>
+        <v>5.1143</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.615331</v>
+        <v>-1.287247</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.615518</v>
+        <v>-1.287396</v>
       </c>
     </row>
     <row r="24">
@@ -1034,16 +1034,16 @@
         <v>44804</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D28" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E28" t="n">
         <v>8.727061000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>4.443025</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="29">
@@ -1078,16 +1078,16 @@
         <v>44804</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
         <v>8.825751</v>
       </c>
       <c r="F30" t="n">
-        <v>4.098046</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="31">
@@ -1128,7 +1128,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.002811</v>
+        <v>0.002704</v>
       </c>
       <c r="F32" t="n">
         <v>-0.000124</v>
@@ -1150,7 +1150,7 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002811</v>
+        <v>0.002704</v>
       </c>
       <c r="F33" t="n">
         <v>-0.000124</v>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,29 +609,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>97.10569</v>
+        <v>5.4394</v>
       </c>
       <c r="F9" t="n">
-        <v>109.89427</v>
+        <v>5.1149</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1149</v>
+        <v>5.1143</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1143</v>
+        <v>7372243</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="F12" t="n">
-        <v>7372243</v>
+        <v>2731513</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F13" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F14" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.34</v>
+        <v>3.01</v>
       </c>
       <c r="F15" t="n">
-        <v>4.88</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,471 +776,383 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>21.42</v>
       </c>
       <c r="F16" t="n">
-        <v>3.31</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>3.01</v>
+        <v>368886</v>
       </c>
       <c r="F17" t="n">
-        <v>5.81</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E18" t="n">
-        <v>21.42</v>
+        <v>0.541272</v>
       </c>
       <c r="F18" t="n">
-        <v>32.08</v>
+        <v>-0.6395690000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D19" t="n">
         <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>368886</v>
+        <v>3.74306</v>
       </c>
       <c r="F19" t="n">
-        <v>372616</v>
+        <v>-1.287247</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E20" t="n">
-        <v>0.541272</v>
+        <v>3.743473</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6395690000000001</v>
+        <v>-1.287396</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.59426</v>
+        <v>1.596467</v>
       </c>
       <c r="F21" t="n">
-        <v>0.332557</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>3.74306</v>
+        <v>0.888065</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.287247</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>3.743473</v>
+        <v>2.123375</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.287396</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>1.596467</v>
+        <v>-0.259972</v>
       </c>
       <c r="F24" t="n">
-        <v>0.257708</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E25" t="n">
-        <v>0.888065</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.694824</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E26" t="n">
-        <v>2.123375</v>
+        <v>8.58755</v>
       </c>
       <c r="F26" t="n">
-        <v>0.826955</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.259972</v>
+        <v>8.825751</v>
       </c>
       <c r="F27" t="n">
-        <v>0.777299</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E28" t="n">
-        <v>8.727061000000001</v>
+        <v>1.5</v>
       </c>
       <c r="F28" t="n">
-        <v>4.223453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>8.58755</v>
+        <v>0.002704</v>
       </c>
       <c r="F29" t="n">
-        <v>2.178243</v>
+        <v>-0.000124</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>8.825751</v>
+        <v>0.002704</v>
       </c>
       <c r="F30" t="n">
-        <v>3.983297</v>
+        <v>-0.000124</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E31" t="n">
-        <v>1.5</v>
+        <v>-0.01</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.002704</v>
+        <v>-0.02</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000124</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002704</v>
+        <v>1.47</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000124</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_total</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D34" t="n">
-        <v>58</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D35" t="n">
-        <v>58</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,29 +609,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46295</v>
+        <v>46203</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>5.4394</v>
+        <v>97.10569</v>
       </c>
       <c r="F9" t="n">
-        <v>5.1149</v>
+        <v>109.89427</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4388</v>
+        <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1143</v>
+        <v>5.0918</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4441056</v>
+        <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>7372243</v>
+        <v>5.0912</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1894119</v>
+        <v>4441056</v>
       </c>
       <c r="F12" t="n">
-        <v>2731513</v>
+        <v>7372243</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F13" t="n">
-        <v>4640730</v>
+        <v>2731513</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F14" t="n">
-        <v>4.88</v>
+        <v>4640730</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>3.01</v>
+        <v>2.34</v>
       </c>
       <c r="F15" t="n">
-        <v>5.81</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,383 +776,471 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>21.42</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>32.08</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>368886</v>
+        <v>3.01</v>
       </c>
       <c r="F17" t="n">
-        <v>372616</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>0.541272</v>
+        <v>21.42</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6395690000000001</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
         <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>3.74306</v>
+        <v>368886</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.287247</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46295</v>
+        <v>46203</v>
       </c>
       <c r="D20" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>3.743473</v>
+        <v>0.541272</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.287396</v>
+        <v>-0.6395690000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>1.596467</v>
+        <v>-0.59426</v>
       </c>
       <c r="F21" t="n">
-        <v>0.257708</v>
+        <v>0.332557</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>0.888065</v>
+        <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.694824</v>
+        <v>-1.733055</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>2.123375</v>
+        <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>0.826955</v>
+        <v>-1.733256</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D24" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.259972</v>
+        <v>1.596467</v>
       </c>
       <c r="F24" t="n">
-        <v>0.777299</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D25" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>8.727061000000001</v>
+        <v>0.888065</v>
       </c>
       <c r="F25" t="n">
-        <v>4.223453</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D26" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>8.58755</v>
+        <v>2.123375</v>
       </c>
       <c r="F26" t="n">
-        <v>2.178243</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>8.825751</v>
+        <v>-0.259972</v>
       </c>
       <c r="F27" t="n">
-        <v>3.983297</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>0.002704</v>
+        <v>8.58755</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.000124</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>0.002704</v>
+        <v>8.825751</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000124</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D31" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.01</v>
+        <v>1.5</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.02</v>
+        <v>0.002704</v>
       </c>
       <c r="F32" t="n">
-        <v>0.39</v>
+        <v>-0.000124</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>dif_cdi</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D33" t="n">
+        <v>60</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.002704</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.000124</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_total</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D34" t="n">
+        <v>58</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D35" t="n">
+        <v>58</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>dif_juros_credito_total</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D33" t="n">
+      <c r="B37" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D37" t="n">
         <v>58</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E37" t="n">
         <v>1.47</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,7 +521,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,16 +534,16 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>1.16</v>
+        <v>-0.64</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.32</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -556,38 +556,38 @@
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.64</v>
+        <v>1.2</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.22</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2</v>
+        <v>96.95313</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.32</v>
+        <v>110.22154</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>96.95313</v>
+        <v>97.10569</v>
       </c>
       <c r="F8" t="n">
-        <v>110.22154</v>
+        <v>109.89427</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>97.10569</v>
+        <v>5.4394</v>
       </c>
       <c r="F9" t="n">
-        <v>109.89427</v>
+        <v>5.0918</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0918</v>
+        <v>5.0912</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0912</v>
+        <v>7372243</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="F12" t="n">
-        <v>7372243</v>
+        <v>2731513</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F13" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F14" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="F16" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="F17" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="F18" t="n">
-        <v>32.08</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>368886</v>
+        <v>0.541272</v>
       </c>
       <c r="F19" t="n">
-        <v>372616</v>
+        <v>-0.6395690000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>0.541272</v>
+        <v>-0.59426</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6395690000000001</v>
+        <v>0.332557</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.59426</v>
+        <v>3.74306</v>
       </c>
       <c r="F21" t="n">
-        <v>0.332557</v>
+        <v>-1.733055</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.733055</v>
+        <v>-1.733256</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.733256</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="F24" t="n">
-        <v>0.257708</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.694824</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2.123375</v>
+        <v>-0.259972</v>
       </c>
       <c r="F26" t="n">
-        <v>0.826955</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.259972</v>
+        <v>8.58755</v>
       </c>
       <c r="F27" t="n">
-        <v>0.777299</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="F28" t="n">
-        <v>4.223453</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>8.58755</v>
+        <v>1.5</v>
       </c>
       <c r="F29" t="n">
-        <v>2.178243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>8.825751</v>
+        <v>0.002704</v>
       </c>
       <c r="F30" t="n">
-        <v>3.983297</v>
+        <v>-0.000124</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>1.5</v>
+        <v>0.002704</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.000124</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.002704</v>
+        <v>-0.01</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000124</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002704</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000124</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="F35" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02154</v>
+        <v>0.021664</v>
       </c>
       <c r="F3" t="n">
         <v>0.05166</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02154</v>
+        <v>0.021664</v>
       </c>
       <c r="F4" t="n">
         <v>0.05166</v>
@@ -521,7 +521,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,16 +534,16 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.22</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -556,38 +556,38 @@
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2</v>
+        <v>-0.64</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.32</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>96.95313</v>
+        <v>1.2</v>
       </c>
       <c r="F7" t="n">
-        <v>110.22154</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>97.10569</v>
+        <v>96.95313</v>
       </c>
       <c r="F8" t="n">
-        <v>109.89427</v>
+        <v>110.22154</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46295</v>
+        <v>46203</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>5.4394</v>
+        <v>97.10569</v>
       </c>
       <c r="F9" t="n">
-        <v>5.0918</v>
+        <v>109.89427</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4388</v>
+        <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0912</v>
+        <v>5.0918</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4441056</v>
+        <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>7372243</v>
+        <v>5.0912</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1894119</v>
+        <v>4441056</v>
       </c>
       <c r="F12" t="n">
-        <v>2731513</v>
+        <v>7372243</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F13" t="n">
-        <v>4640730</v>
+        <v>2731513</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F14" t="n">
-        <v>4.88</v>
+        <v>4640730</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="F15" t="n">
-        <v>3.31</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>5.81</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>21.42</v>
+        <v>3.01</v>
       </c>
       <c r="F17" t="n">
-        <v>32.08</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>368886</v>
+        <v>21.42</v>
       </c>
       <c r="F18" t="n">
-        <v>372616</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>0.541272</v>
+        <v>368886</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6395690000000001</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.59426</v>
+        <v>0.541272</v>
       </c>
       <c r="F20" t="n">
-        <v>0.332557</v>
+        <v>-0.6395690000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46295</v>
+        <v>46203</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>3.74306</v>
+        <v>-0.59426</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.733055</v>
+        <v>0.332557</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>3.743473</v>
+        <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.733256</v>
+        <v>-1.733055</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.596467</v>
+        <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>0.257708</v>
+        <v>-1.733256</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>0.888065</v>
+        <v>1.596467</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.694824</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.123375</v>
+        <v>0.888065</v>
       </c>
       <c r="F25" t="n">
-        <v>0.826955</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.259972</v>
+        <v>2.123375</v>
       </c>
       <c r="F26" t="n">
-        <v>0.777299</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>8.58755</v>
+        <v>-0.259972</v>
       </c>
       <c r="F27" t="n">
-        <v>2.178243</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.825751</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>3.983297</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5</v>
+        <v>8.58755</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>0.002704</v>
+        <v>8.825751</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000124</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.002704</v>
+        <v>1.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.01</v>
+        <v>0.00258</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3</v>
+        <v>-0.000124</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.00258</v>
       </c>
       <c r="F33" t="n">
-        <v>0.13</v>
+        <v>-0.000124</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F34" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>1.47</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.021664</v>
+        <v>0.021808</v>
       </c>
       <c r="F3" t="n">
         <v>0.05166</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.021664</v>
+        <v>0.021808</v>
       </c>
       <c r="F4" t="n">
         <v>0.05166</v>
@@ -647,7 +647,7 @@
         <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0918</v>
+        <v>5.1696</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0912</v>
+        <v>5.169</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.733055</v>
+        <v>-0.231589</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.733256</v>
+        <v>-0.231616</v>
       </c>
     </row>
     <row r="24">
@@ -1128,7 +1128,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00258</v>
+        <v>0.002435</v>
       </c>
       <c r="F32" t="n">
         <v>-0.000124</v>
@@ -1150,7 +1150,7 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.00258</v>
+        <v>0.002435</v>
       </c>
       <c r="F33" t="n">
         <v>-0.000124</v>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.021808</v>
+        <v>0.021979</v>
       </c>
       <c r="F3" t="n">
         <v>0.05166</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.021808</v>
+        <v>0.021979</v>
       </c>
       <c r="F4" t="n">
         <v>0.05166</v>
@@ -594,16 +594,16 @@
         <v>44469</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>96.95313</v>
+        <v>96.96513</v>
       </c>
       <c r="F8" t="n">
-        <v>110.22154</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="9">
@@ -616,16 +616,16 @@
         <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>97.10569</v>
+        <v>97.10777</v>
       </c>
       <c r="F9" t="n">
-        <v>109.89427</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1696</v>
+        <v>5.149</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>5.169</v>
+        <v>5.1484</v>
       </c>
     </row>
     <row r="12">
@@ -858,16 +858,16 @@
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>0.541272</v>
+        <v>0.537905</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6395690000000001</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="21">
@@ -880,16 +880,16 @@
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.59426</v>
+        <v>-0.594556</v>
       </c>
       <c r="F21" t="n">
-        <v>0.332557</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="22">
@@ -911,7 +911,7 @@
         <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.231589</v>
+        <v>-0.629149</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.231616</v>
+        <v>-0.6292219999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1128,7 +1128,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.002435</v>
+        <v>0.002265</v>
       </c>
       <c r="F32" t="n">
         <v>-0.000124</v>
@@ -1150,7 +1150,7 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002435</v>
+        <v>0.002265</v>
       </c>
       <c r="F33" t="n">
         <v>-0.000124</v>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -471,7 +471,7 @@
         <v>6.25</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.021979</v>
+        <v>0.022184</v>
       </c>
       <c r="F3" t="n">
         <v>0.05166</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.021979</v>
+        <v>0.022184</v>
       </c>
       <c r="F4" t="n">
         <v>0.05166</v>
@@ -647,7 +647,7 @@
         <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.149</v>
+        <v>5.1527</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1484</v>
+        <v>5.152</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.629149</v>
+        <v>-0.557743</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6292219999999999</v>
+        <v>-0.559738</v>
       </c>
     </row>
     <row r="24">
@@ -1109,7 +1109,7 @@
         <v>1.5</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="32">
@@ -1128,7 +1128,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.002265</v>
+        <v>0.00206</v>
       </c>
       <c r="F32" t="n">
         <v>-0.000124</v>
@@ -1150,7 +1150,7 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002265</v>
+        <v>0.00206</v>
       </c>
       <c r="F33" t="n">
         <v>-0.000124</v>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -490,38 +490,38 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.022184</v>
+        <v>0.022435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05166</v>
+        <v>0.051587</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>0.022184</v>
+        <v>-0.64</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05166</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,7 +534,7 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="F5" t="n">
         <v>-0.32</v>
@@ -543,139 +543,139 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.64</v>
+        <v>96.96513</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.22</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2</v>
+        <v>97.10777</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.32</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D8" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>96.96513</v>
+        <v>5.4394</v>
       </c>
       <c r="F8" t="n">
-        <v>109.91611</v>
+        <v>5.1521</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>97.10777</v>
+        <v>5.4388</v>
       </c>
       <c r="F9" t="n">
-        <v>114.40189</v>
+        <v>5.1515</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4394</v>
+        <v>1894119</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1527</v>
+        <v>2731513</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.4388</v>
+        <v>2546936</v>
       </c>
       <c r="F11" t="n">
-        <v>5.152</v>
+        <v>4640730</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4441056</v>
+        <v>2.34</v>
       </c>
       <c r="F12" t="n">
-        <v>7372243</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1894119</v>
+        <v>1.43</v>
       </c>
       <c r="F13" t="n">
-        <v>2731513</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,126 +732,126 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2546936</v>
+        <v>21.42</v>
       </c>
       <c r="F14" t="n">
-        <v>4640730</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>2.34</v>
+        <v>368886</v>
       </c>
       <c r="F15" t="n">
-        <v>4.88</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>0.537905</v>
       </c>
       <c r="F16" t="n">
-        <v>3.31</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" t="n">
-        <v>3.01</v>
+        <v>-0.594556</v>
       </c>
       <c r="F17" t="n">
-        <v>5.81</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>21.42</v>
+        <v>3.74306</v>
       </c>
       <c r="F18" t="n">
-        <v>32.08</v>
+        <v>-0.569322</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D19" t="n">
         <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>368886</v>
+        <v>3.743473</v>
       </c>
       <c r="F19" t="n">
-        <v>372616</v>
+        <v>-0.569388</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,16 +864,16 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>0.537905</v>
+        <v>0.888065</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.219358</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
@@ -886,361 +886,185 @@
         <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.594556</v>
+        <v>2.123375</v>
       </c>
       <c r="F21" t="n">
-        <v>4.057001</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" t="n">
-        <v>3.74306</v>
+        <v>-0.259972</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.557743</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E23" t="n">
-        <v>3.743473</v>
+        <v>8.58755</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.559738</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E24" t="n">
-        <v>1.596467</v>
+        <v>8.825751</v>
       </c>
       <c r="F24" t="n">
-        <v>0.257708</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E25" t="n">
-        <v>0.888065</v>
+        <v>1.5</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.694824</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E26" t="n">
-        <v>2.123375</v>
+        <v>0.001809</v>
       </c>
       <c r="F26" t="n">
-        <v>0.826955</v>
+        <v>-0.000197</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.259972</v>
+        <v>-0.01</v>
       </c>
       <c r="F27" t="n">
-        <v>0.777299</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E28" t="n">
-        <v>8.727061000000001</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>4.223453</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E29" t="n">
-        <v>8.58755</v>
+        <v>1.47</v>
       </c>
       <c r="F29" t="n">
-        <v>2.178243</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>inpc_acum_12m</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>44804</v>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D30" t="n">
-        <v>49</v>
-      </c>
-      <c r="E30" t="n">
-        <v>8.825751</v>
-      </c>
-      <c r="F30" t="n">
-        <v>3.983297</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>dif_selic_meta</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D31" t="n">
-        <v>60</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F31" t="n">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>dif_selic_over</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D32" t="n">
-        <v>60</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.00206</v>
-      </c>
-      <c r="F32" t="n">
-        <v>-0.000124</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>dif_cdi</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D33" t="n">
-        <v>60</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.00206</v>
-      </c>
-      <c r="F33" t="n">
-        <v>-0.000124</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_total</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D34" t="n">
-        <v>58</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D35" t="n">
-        <v>58</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -493,35 +493,35 @@
         <v>0.022435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051587</v>
+        <v>0.051526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.64</v>
+        <v>0.022435</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.22</v>
+        <v>0.051587</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,7 +534,7 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="F5" t="n">
         <v>-0.32</v>
@@ -543,73 +543,73 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>96.96513</v>
+        <v>-0.64</v>
       </c>
       <c r="F6" t="n">
-        <v>109.91611</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>97.10777</v>
+        <v>1.2</v>
       </c>
       <c r="F7" t="n">
-        <v>114.40189</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>5.4394</v>
+        <v>96.96513</v>
       </c>
       <c r="F8" t="n">
-        <v>5.1521</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -622,38 +622,38 @@
         <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>5.4388</v>
+        <v>5.4394</v>
       </c>
       <c r="F9" t="n">
-        <v>5.1515</v>
+        <v>5.1575</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>1894119</v>
+        <v>5.4388</v>
       </c>
       <c r="F10" t="n">
-        <v>2731513</v>
+        <v>5.1569</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -666,16 +666,16 @@
         <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>2546936</v>
+        <v>4441056</v>
       </c>
       <c r="F11" t="n">
-        <v>4640730</v>
+        <v>7372243</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>2.34</v>
+        <v>1894119</v>
       </c>
       <c r="F12" t="n">
-        <v>4.88</v>
+        <v>2731513</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1.43</v>
+        <v>2546936</v>
       </c>
       <c r="F13" t="n">
-        <v>3.31</v>
+        <v>4640730</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,339 +732,471 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>21.42</v>
+        <v>2.34</v>
       </c>
       <c r="F14" t="n">
-        <v>32.08</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>368886</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>372616</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D16" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>0.537905</v>
+        <v>3.01</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.219358</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D17" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.594556</v>
+        <v>21.42</v>
       </c>
       <c r="F17" t="n">
-        <v>4.057001</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>3.74306</v>
+        <v>368886</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.569322</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>3.743473</v>
+        <v>0.537905</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.569388</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E20" t="n">
-        <v>0.888065</v>
+        <v>3.74306</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.694824</v>
+        <v>-0.465107</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>2.123375</v>
+        <v>3.743473</v>
       </c>
       <c r="F21" t="n">
-        <v>0.826955</v>
+        <v>-0.465161</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D22" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.259972</v>
+        <v>1.596467</v>
       </c>
       <c r="F22" t="n">
-        <v>0.777299</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>8.58755</v>
+        <v>0.888065</v>
       </c>
       <c r="F23" t="n">
-        <v>2.178243</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D24" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>8.825751</v>
+        <v>2.123375</v>
       </c>
       <c r="F24" t="n">
-        <v>3.983297</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D25" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5</v>
+        <v>-0.259972</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.25</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E26" t="n">
-        <v>0.001809</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.000197</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.01</v>
+        <v>8.58755</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D28" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>8.825751</v>
       </c>
       <c r="F28" t="n">
-        <v>0.13</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>dif_selic_meta</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D29" t="n">
+        <v>60</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>dif_selic_over</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D30" t="n">
+        <v>60</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.001809</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.000259</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>dif_cdi</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D31" t="n">
+        <v>60</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.001809</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.000197</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_total</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D32" t="n">
+        <v>58</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D33" t="n">
+        <v>58</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D34" t="n">
+        <v>58</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>dif_juros_credito_total</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D29" t="n">
+      <c r="B35" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D35" t="n">
         <v>58</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E35" t="n">
         <v>1.47</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F35" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,29 +609,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>5.4394</v>
+        <v>97.10777</v>
       </c>
       <c r="F9" t="n">
-        <v>5.1575</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4388</v>
+        <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1569</v>
+        <v>5.1575</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4441056</v>
+        <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>7372243</v>
+        <v>5.1569</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1894119</v>
+        <v>4441056</v>
       </c>
       <c r="F12" t="n">
-        <v>2731513</v>
+        <v>7372243</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F13" t="n">
-        <v>4640730</v>
+        <v>2731513</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F14" t="n">
-        <v>4.88</v>
+        <v>4640730</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="F15" t="n">
-        <v>3.31</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>5.81</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,148 +798,148 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>21.42</v>
+        <v>3.01</v>
       </c>
       <c r="F17" t="n">
-        <v>32.08</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>368886</v>
+        <v>21.42</v>
       </c>
       <c r="F18" t="n">
-        <v>372616</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>0.537905</v>
+        <v>368886</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.219358</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D20" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>3.74306</v>
+        <v>0.537905</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.465107</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>3.743473</v>
+        <v>-0.594556</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.465161</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>1.596467</v>
+        <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>0.257708</v>
+        <v>-0.465107</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>0.888065</v>
+        <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.694824</v>
+        <v>-0.465161</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,82 +952,82 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>2.123375</v>
+        <v>1.596467</v>
       </c>
       <c r="F24" t="n">
-        <v>0.826955</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.259972</v>
+        <v>0.888065</v>
       </c>
       <c r="F25" t="n">
-        <v>0.777299</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D26" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>8.727061000000001</v>
+        <v>2.123375</v>
       </c>
       <c r="F26" t="n">
-        <v>4.223453</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>8.58755</v>
+        <v>-0.259972</v>
       </c>
       <c r="F27" t="n">
-        <v>2.178243</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.825751</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>3.983297</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5</v>
+        <v>8.58755</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.25</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>0.001809</v>
+        <v>8.825751</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000259</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001809</v>
+        <v>1.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000197</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.01</v>
+        <v>0.001809</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3</v>
+        <v>-0.000259</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.001809</v>
       </c>
       <c r="F33" t="n">
-        <v>0.13</v>
+        <v>-0.000197</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F34" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>1.47</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.022435</v>
+        <v>0.022748</v>
       </c>
       <c r="F3" t="n">
         <v>0.051526</v>
@@ -512,10 +512,10 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.022435</v>
+        <v>0.022748</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051587</v>
+        <v>0.051526</v>
       </c>
     </row>
     <row r="5">
@@ -565,29 +565,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2</v>
+        <v>96.96513</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.32</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>96.96513</v>
+        <v>97.10777</v>
       </c>
       <c r="F8" t="n">
-        <v>109.91611</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>97.10777</v>
+        <v>5.4394</v>
       </c>
       <c r="F9" t="n">
-        <v>114.40189</v>
+        <v>5.1575</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1575</v>
+        <v>5.1569</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1569</v>
+        <v>7372243</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="F12" t="n">
-        <v>7372243</v>
+        <v>2731513</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F13" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F14" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="F16" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="F17" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="F18" t="n">
-        <v>32.08</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>368886</v>
+        <v>0.537905</v>
       </c>
       <c r="F19" t="n">
-        <v>372616</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>0.537905</v>
+        <v>-0.594556</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.594556</v>
+        <v>3.74306</v>
       </c>
       <c r="F21" t="n">
-        <v>4.057001</v>
+        <v>-0.465107</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.465107</v>
+        <v>-0.465161</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.465161</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="F24" t="n">
-        <v>0.257708</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.694824</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2.123375</v>
+        <v>-0.259972</v>
       </c>
       <c r="F26" t="n">
-        <v>0.826955</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.259972</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.777299</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.727061000000001</v>
+        <v>8.58755</v>
       </c>
       <c r="F28" t="n">
-        <v>4.223453</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>8.58755</v>
+        <v>1.5</v>
       </c>
       <c r="F29" t="n">
-        <v>2.178243</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>8.825751</v>
+        <v>0.001496</v>
       </c>
       <c r="F30" t="n">
-        <v>3.983297</v>
+        <v>-0.000259</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>1.5</v>
+        <v>0.001496</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.25</v>
+        <v>-0.000259</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001809</v>
+        <v>-0.01</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000259</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001809</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000197</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="F35" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,10 +490,10 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.022748</v>
+        <v>0.02315</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051526</v>
+        <v>0.051473</v>
       </c>
     </row>
     <row r="4">
@@ -512,10 +512,10 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.022748</v>
+        <v>0.02315</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051526</v>
+        <v>0.051473</v>
       </c>
     </row>
     <row r="5">
@@ -565,29 +565,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>96.96513</v>
+        <v>1.2</v>
       </c>
       <c r="F7" t="n">
-        <v>109.91611</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>97.10777</v>
+        <v>96.96513</v>
       </c>
       <c r="F8" t="n">
-        <v>114.40189</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>5.4394</v>
+        <v>97.10777</v>
       </c>
       <c r="F9" t="n">
-        <v>5.1575</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4388</v>
+        <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1569</v>
+        <v>5.1117</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4441056</v>
+        <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>7372243</v>
+        <v>5.1111</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1894119</v>
+        <v>4441056</v>
       </c>
       <c r="F12" t="n">
-        <v>2731513</v>
+        <v>7372243</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F13" t="n">
-        <v>4640730</v>
+        <v>2731513</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F14" t="n">
-        <v>4.88</v>
+        <v>4640730</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="F15" t="n">
-        <v>3.31</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>5.81</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>21.42</v>
+        <v>3.01</v>
       </c>
       <c r="F17" t="n">
-        <v>32.08</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>368886</v>
+        <v>21.42</v>
       </c>
       <c r="F18" t="n">
-        <v>372616</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>0.537905</v>
+        <v>368886</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.219358</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.594556</v>
+        <v>0.537905</v>
       </c>
       <c r="F20" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>3.74306</v>
+        <v>-0.594556</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.465107</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>3.743473</v>
+        <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.465161</v>
+        <v>-1.349004</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.596467</v>
+        <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>0.257708</v>
+        <v>-1.34916</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>0.888065</v>
+        <v>1.596467</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.694824</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.123375</v>
+        <v>0.888065</v>
       </c>
       <c r="F25" t="n">
-        <v>0.826955</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.259972</v>
+        <v>2.123375</v>
       </c>
       <c r="F26" t="n">
-        <v>0.777299</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>8.727061000000001</v>
+        <v>-0.259972</v>
       </c>
       <c r="F27" t="n">
-        <v>4.223453</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.58755</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>2.178243</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5</v>
+        <v>8.58755</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.25</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>0.001496</v>
+        <v>8.825751</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000259</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001496</v>
+        <v>1.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000259</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.01</v>
+        <v>0.001094</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3</v>
+        <v>-0.000311</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.001094</v>
       </c>
       <c r="F33" t="n">
-        <v>0.13</v>
+        <v>-0.000311</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F34" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>1.47</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,7 +697,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F13" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F14" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="F16" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="F17" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="F18" t="n">
-        <v>32.08</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>368886</v>
+        <v>0.537905</v>
       </c>
       <c r="F19" t="n">
-        <v>372616</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>0.537905</v>
+        <v>-0.594556</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.594556</v>
+        <v>3.74306</v>
       </c>
       <c r="F21" t="n">
-        <v>4.057001</v>
+        <v>-1.349004</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.349004</v>
+        <v>-1.34916</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.34916</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,82 +952,82 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.596467</v>
+        <v>2.123375</v>
       </c>
       <c r="F24" t="n">
-        <v>0.257708</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>0.888065</v>
+        <v>-0.259972</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.694824</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E26" t="n">
-        <v>2.123375</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.826955</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.259972</v>
+        <v>8.58755</v>
       </c>
       <c r="F27" t="n">
-        <v>0.777299</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="F28" t="n">
-        <v>4.223453</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>8.58755</v>
+        <v>1.5</v>
       </c>
       <c r="F29" t="n">
-        <v>2.178243</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>8.825751</v>
+        <v>0.001094</v>
       </c>
       <c r="F30" t="n">
-        <v>3.983297</v>
+        <v>-0.000311</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>1.5</v>
+        <v>0.001094</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.25</v>
+        <v>-0.000311</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001094</v>
+        <v>-0.01</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000311</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001094</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000311</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="F35" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,10 +490,10 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02315</v>
+        <v>0.023687</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051473</v>
+        <v>0.051427</v>
       </c>
     </row>
     <row r="4">
@@ -512,10 +512,10 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02315</v>
+        <v>0.023687</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051473</v>
+        <v>0.051427</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1117</v>
+        <v>5.1161</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1111</v>
+        <v>5.1155</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +697,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F13" t="n">
-        <v>4640730</v>
+        <v>2731513</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F14" t="n">
-        <v>4.88</v>
+        <v>4640730</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="F15" t="n">
-        <v>3.31</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>5.81</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>21.42</v>
+        <v>3.01</v>
       </c>
       <c r="F17" t="n">
-        <v>32.08</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>368886</v>
+        <v>21.42</v>
       </c>
       <c r="F18" t="n">
-        <v>372616</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>0.537905</v>
+        <v>368886</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.219358</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.594556</v>
+        <v>0.537905</v>
       </c>
       <c r="F20" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>3.74306</v>
+        <v>-0.594556</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.349004</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>3.743473</v>
+        <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.34916</v>
+        <v>-1.264088</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.596467</v>
+        <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>0.257708</v>
+        <v>-1.264235</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,82 +952,82 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>2.123375</v>
+        <v>1.596467</v>
       </c>
       <c r="F24" t="n">
-        <v>0.826955</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.259972</v>
+        <v>0.888065</v>
       </c>
       <c r="F25" t="n">
-        <v>0.777299</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D26" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>8.727061000000001</v>
+        <v>2.123375</v>
       </c>
       <c r="F26" t="n">
-        <v>4.223453</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>8.58755</v>
+        <v>-0.259972</v>
       </c>
       <c r="F27" t="n">
-        <v>2.178243</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.825751</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>3.983297</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5</v>
+        <v>8.58755</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.25</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>0.001094</v>
+        <v>8.825751</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000311</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001094</v>
+        <v>1.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000311</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.01</v>
+        <v>0.000557</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3</v>
+        <v>-0.000357</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.000557</v>
       </c>
       <c r="F33" t="n">
-        <v>0.13</v>
+        <v>-0.000357</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F34" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>1.47</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -493,7 +493,7 @@
         <v>0.023687</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051427</v>
+        <v>0.051387</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>0.023687</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051427</v>
+        <v>0.051387</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1161</v>
+        <v>5.1414</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1155</v>
+        <v>5.1408</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.264088</v>
+        <v>-0.775822</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.264235</v>
+        <v>-0.775912</v>
       </c>
     </row>
     <row r="24">
@@ -1131,7 +1131,7 @@
         <v>0.000557</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000357</v>
+        <v>-0.000397</v>
       </c>
     </row>
     <row r="33">
@@ -1153,7 +1153,7 @@
         <v>0.000557</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000357</v>
+        <v>-0.000397</v>
       </c>
     </row>
     <row r="34">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -493,7 +493,7 @@
         <v>0.023687</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051387</v>
+        <v>0.051352</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>0.023687</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051387</v>
+        <v>0.051352</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1414</v>
+        <v>5.1795</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1408</v>
+        <v>5.1789</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.775822</v>
+        <v>-0.040528</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.775912</v>
+        <v>-0.040533</v>
       </c>
     </row>
     <row r="24">
@@ -1131,7 +1131,7 @@
         <v>0.000557</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000397</v>
+        <v>-0.000432</v>
       </c>
     </row>
     <row r="33">
@@ -1153,7 +1153,7 @@
         <v>0.000557</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000397</v>
+        <v>-0.000432</v>
       </c>
     </row>
     <row r="34">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
         <v>0.023687</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051352</v>
+        <v>0.051321</v>
       </c>
     </row>
     <row r="4">
@@ -647,35 +647,35 @@
         <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1795</v>
+        <v>5.1991</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1789</v>
+        <v>7372243</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="F12" t="n">
-        <v>7372243</v>
+        <v>2731513</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F13" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F14" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="F16" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="F17" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="F18" t="n">
-        <v>32.08</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>368886</v>
+        <v>0.537905</v>
       </c>
       <c r="F19" t="n">
-        <v>372616</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,82 +864,82 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>0.537905</v>
+        <v>-0.594556</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.594556</v>
+        <v>3.74306</v>
       </c>
       <c r="F21" t="n">
-        <v>4.057001</v>
+        <v>0.337734</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>3.74306</v>
+        <v>1.596467</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.040528</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>3.743473</v>
+        <v>0.888065</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.040533</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,82 +952,82 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.596467</v>
+        <v>2.123375</v>
       </c>
       <c r="F24" t="n">
-        <v>0.257708</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>0.888065</v>
+        <v>-0.259972</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.694824</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E26" t="n">
-        <v>2.123375</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.826955</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.259972</v>
+        <v>8.58755</v>
       </c>
       <c r="F27" t="n">
-        <v>0.777299</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="F28" t="n">
-        <v>4.223453</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>8.58755</v>
+        <v>1.5</v>
       </c>
       <c r="F29" t="n">
-        <v>2.178243</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>8.825751</v>
+        <v>0.000557</v>
       </c>
       <c r="F30" t="n">
-        <v>3.983297</v>
+        <v>-0.000464</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>1.5</v>
+        <v>0.000557</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.25</v>
+        <v>-0.000432</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.000557</v>
+        <v>-0.01</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000432</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000557</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000432</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="F35" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -653,29 +653,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4441056</v>
+        <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>7372243</v>
+        <v>5.1985</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1894119</v>
+        <v>4441056</v>
       </c>
       <c r="F12" t="n">
-        <v>2731513</v>
+        <v>7372243</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F13" t="n">
-        <v>4640730</v>
+        <v>2731513</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F14" t="n">
-        <v>4.88</v>
+        <v>4640730</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="F15" t="n">
-        <v>3.31</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>5.81</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>21.42</v>
+        <v>3.01</v>
       </c>
       <c r="F17" t="n">
-        <v>32.08</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>368886</v>
+        <v>21.42</v>
       </c>
       <c r="F18" t="n">
-        <v>372616</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>0.537905</v>
+        <v>368886</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.219358</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,82 +864,82 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.594556</v>
+        <v>0.537905</v>
       </c>
       <c r="F20" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>3.74306</v>
+        <v>-0.594556</v>
       </c>
       <c r="F21" t="n">
-        <v>0.337734</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>1.596467</v>
+        <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>0.257708</v>
+        <v>0.337734</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>0.888065</v>
+        <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.694824</v>
+        <v>0.337773</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,82 +952,82 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>2.123375</v>
+        <v>1.596467</v>
       </c>
       <c r="F24" t="n">
-        <v>0.826955</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.259972</v>
+        <v>0.888065</v>
       </c>
       <c r="F25" t="n">
-        <v>0.777299</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D26" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>8.727061000000001</v>
+        <v>2.123375</v>
       </c>
       <c r="F26" t="n">
-        <v>4.223453</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>8.58755</v>
+        <v>-0.259972</v>
       </c>
       <c r="F27" t="n">
-        <v>2.178243</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.825751</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>3.983297</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5</v>
+        <v>8.58755</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.25</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>0.000557</v>
+        <v>8.825751</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000464</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.000557</v>
+        <v>1.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000432</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.01</v>
+        <v>0.000557</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3</v>
+        <v>-0.000464</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.000557</v>
       </c>
       <c r="F33" t="n">
-        <v>0.13</v>
+        <v>-0.000432</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F34" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>1.47</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -829,29 +829,29 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>368886</v>
+        <v>0.537905</v>
       </c>
       <c r="F19" t="n">
-        <v>372616</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>0.537905</v>
+        <v>-0.594556</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.594556</v>
+        <v>3.74306</v>
       </c>
       <c r="F21" t="n">
-        <v>4.057001</v>
+        <v>0.337734</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="F22" t="n">
-        <v>0.337734</v>
+        <v>0.337773</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="F23" t="n">
-        <v>0.337773</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="F24" t="n">
-        <v>0.257708</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.694824</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E26" t="n">
-        <v>2.123375</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.826955</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.259972</v>
+        <v>8.58755</v>
       </c>
       <c r="F27" t="n">
-        <v>0.777299</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="F28" t="n">
-        <v>4.223453</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>8.58755</v>
+        <v>1.5</v>
       </c>
       <c r="F29" t="n">
-        <v>2.178243</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>8.825751</v>
+        <v>0.000557</v>
       </c>
       <c r="F30" t="n">
-        <v>3.983297</v>
+        <v>-0.000464</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>1.5</v>
+        <v>0.000557</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.25</v>
+        <v>-0.000432</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.000557</v>
+        <v>-0.01</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000464</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000557</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000432</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="F35" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,7 +515,7 @@
         <v>0.023687</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051352</v>
+        <v>0.051321</v>
       </c>
     </row>
     <row r="5">
@@ -669,7 +669,7 @@
         <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1985</v>
+        <v>5.2126</v>
       </c>
     </row>
     <row r="12">
@@ -829,29 +829,29 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>0.537905</v>
+        <v>368886</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.219358</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.594556</v>
+        <v>0.537905</v>
       </c>
       <c r="F20" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>3.74306</v>
+        <v>-0.594556</v>
       </c>
       <c r="F21" t="n">
-        <v>0.337734</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>3.743473</v>
+        <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>0.337773</v>
+        <v>0.337734</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.596467</v>
+        <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>0.257708</v>
+        <v>0.609921</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>0.888065</v>
+        <v>1.596467</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.694824</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.123375</v>
+        <v>0.888065</v>
       </c>
       <c r="F25" t="n">
-        <v>0.826955</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D26" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>8.727061000000001</v>
+        <v>2.123375</v>
       </c>
       <c r="F26" t="n">
-        <v>4.223453</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>8.58755</v>
+        <v>-0.259972</v>
       </c>
       <c r="F27" t="n">
-        <v>2.178243</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.825751</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>3.983297</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5</v>
+        <v>8.58755</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.25</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>0.000557</v>
+        <v>8.825751</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000464</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.000557</v>
+        <v>1.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000432</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.01</v>
+        <v>0.000557</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3</v>
+        <v>-0.000464</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.000557</v>
       </c>
       <c r="F33" t="n">
-        <v>0.13</v>
+        <v>-0.000464</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F34" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>1.47</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,29 +565,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2</v>
+        <v>96.96513</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.32</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>96.96513</v>
+        <v>97.10777</v>
       </c>
       <c r="F8" t="n">
-        <v>109.91611</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>97.10777</v>
+        <v>5.4394</v>
       </c>
       <c r="F9" t="n">
-        <v>114.40189</v>
+        <v>5.1991</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1991</v>
+        <v>5.2126</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="F11" t="n">
-        <v>5.2126</v>
+        <v>7372243</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="F12" t="n">
-        <v>7372243</v>
+        <v>2731513</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F13" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F14" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="F16" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,148 +798,148 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="F17" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" t="n">
-        <v>21.42</v>
+        <v>0.537905</v>
       </c>
       <c r="F18" t="n">
-        <v>32.08</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>368886</v>
+        <v>-0.594556</v>
       </c>
       <c r="F19" t="n">
-        <v>372616</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E20" t="n">
-        <v>0.537905</v>
+        <v>3.74306</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.219358</v>
+        <v>0.337734</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.594556</v>
+        <v>3.743473</v>
       </c>
       <c r="F21" t="n">
-        <v>4.057001</v>
+        <v>0.609921</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>3.74306</v>
+        <v>1.596467</v>
       </c>
       <c r="F22" t="n">
-        <v>0.337734</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>3.743473</v>
+        <v>0.888065</v>
       </c>
       <c r="F23" t="n">
-        <v>0.609921</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,295 +952,207 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.596467</v>
+        <v>2.123375</v>
       </c>
       <c r="F24" t="n">
-        <v>0.257708</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E25" t="n">
-        <v>0.888065</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.694824</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E26" t="n">
-        <v>2.123375</v>
+        <v>8.58755</v>
       </c>
       <c r="F26" t="n">
-        <v>0.826955</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.259972</v>
+        <v>1.5</v>
       </c>
       <c r="F27" t="n">
-        <v>0.777299</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E28" t="n">
-        <v>8.727061000000001</v>
+        <v>0.000557</v>
       </c>
       <c r="F28" t="n">
-        <v>4.223453</v>
+        <v>-0.000464</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>8.58755</v>
+        <v>0.000557</v>
       </c>
       <c r="F29" t="n">
-        <v>2.178243</v>
+        <v>-0.000464</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E30" t="n">
-        <v>8.825751</v>
+        <v>-0.01</v>
       </c>
       <c r="F30" t="n">
-        <v>3.983297</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.25</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.000557</v>
+        <v>-0.02</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000464</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000557</v>
+        <v>1.47</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000464</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_total</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D34" t="n">
-        <v>58</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D35" t="n">
-        <v>58</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
         <v>0.023687</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051321</v>
+        <v>0.051293</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>0.023687</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051321</v>
+        <v>0.051293</v>
       </c>
     </row>
     <row r="5">
@@ -550,44 +550,44 @@
         <v>44469</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
         <v>-0.64</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.22</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>96.96513</v>
+        <v>1.2</v>
       </c>
       <c r="F7" t="n">
-        <v>109.91611</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>97.10777</v>
+        <v>96.96513</v>
       </c>
       <c r="F8" t="n">
-        <v>114.40189</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>5.4394</v>
+        <v>97.10777</v>
       </c>
       <c r="F9" t="n">
-        <v>5.1991</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,516 +644,604 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4388</v>
+        <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.2126</v>
+        <v>5.2132</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4441056</v>
+        <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>7372243</v>
+        <v>5.2126</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12" t="n">
-        <v>1894119</v>
+        <v>4441056</v>
       </c>
       <c r="F12" t="n">
-        <v>2731513</v>
+        <v>7397669</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F13" t="n">
-        <v>4640730</v>
+        <v>2727499</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F14" t="n">
-        <v>4.88</v>
+        <v>4670170</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="F15" t="n">
-        <v>3.31</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>5.81</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>21.42</v>
+        <v>3.01</v>
       </c>
       <c r="F17" t="n">
-        <v>32.08</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>0.537905</v>
+        <v>21.42</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.219358</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.594556</v>
+        <v>368886</v>
       </c>
       <c r="F19" t="n">
-        <v>4.057001</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D20" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>3.74306</v>
+        <v>0.537905</v>
       </c>
       <c r="F20" t="n">
-        <v>0.337734</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>3.743473</v>
+        <v>-0.594556</v>
       </c>
       <c r="F21" t="n">
-        <v>0.609921</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>1.596467</v>
+        <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>0.257708</v>
+        <v>0.60985</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>0.888065</v>
+        <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.694824</v>
+        <v>0.609921</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>2.123375</v>
+        <v>1.596467</v>
       </c>
       <c r="F24" t="n">
-        <v>0.826955</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D25" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>8.727061000000001</v>
+        <v>0.888065</v>
       </c>
       <c r="F25" t="n">
-        <v>4.223453</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>8.58755</v>
+        <v>2.123375</v>
       </c>
       <c r="F26" t="n">
-        <v>2.178243</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>1.5</v>
+        <v>-0.259972</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.25</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>0.000557</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.000464</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E29" t="n">
-        <v>0.000557</v>
+        <v>8.58755</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.000464</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.01</v>
+        <v>8.825751</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D31" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F31" t="n">
-        <v>0.13</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.02</v>
+        <v>0.000557</v>
       </c>
       <c r="F32" t="n">
-        <v>0.39</v>
+        <v>-0.000492</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>dif_cdi</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D33" t="n">
+        <v>60</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.000557</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.000492</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_total</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D34" t="n">
+        <v>59</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D35" t="n">
+        <v>59</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D36" t="n">
+        <v>59</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>dif_juros_credito_total</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D33" t="n">
-        <v>58</v>
-      </c>
-      <c r="E33" t="n">
+      <c r="B37" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D37" t="n">
+        <v>59</v>
+      </c>
+      <c r="E37" t="n">
         <v>1.47</v>
       </c>
-      <c r="F33" t="n">
-        <v>-1.25</v>
+      <c r="F37" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -468,16 +468,16 @@
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>6.25</v>
+        <v>0.023687</v>
       </c>
       <c r="F2" t="n">
-        <v>13.75</v>
+        <v>0.051293</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -499,95 +499,95 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>0.023687</v>
+        <v>1.16</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051293</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E5" t="n">
-        <v>1.16</v>
+        <v>-0.64</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.64</v>
+        <v>1.2</v>
       </c>
       <c r="F6" t="n">
-        <v>1.57</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2</v>
+        <v>96.96513</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.32</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>96.96513</v>
+        <v>97.10777</v>
       </c>
       <c r="F8" t="n">
-        <v>109.91611</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>97.10777</v>
+        <v>5.4394</v>
       </c>
       <c r="F9" t="n">
-        <v>114.40189</v>
+        <v>5.2204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="F10" t="n">
-        <v>5.2132</v>
+        <v>5.2126</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="F11" t="n">
-        <v>5.2126</v>
+        <v>7397669</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>60</v>
       </c>
       <c r="E12" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="F12" t="n">
-        <v>7397669</v>
+        <v>2727499</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F13" t="n">
-        <v>2727499</v>
+        <v>4670170</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F14" t="n">
-        <v>4670170</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>5.04</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="F16" t="n">
-        <v>3.35</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,16 +798,16 @@
         <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="F17" t="n">
-        <v>6.03</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -820,38 +820,38 @@
         <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="F18" t="n">
-        <v>32.26</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>368886</v>
+        <v>0.537905</v>
       </c>
       <c r="F19" t="n">
-        <v>372616</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>0.537905</v>
+        <v>-0.594556</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.594556</v>
+        <v>3.74306</v>
       </c>
       <c r="F21" t="n">
-        <v>4.057001</v>
+        <v>0.748803</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="F22" t="n">
-        <v>0.60985</v>
+        <v>0.609921</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="F23" t="n">
-        <v>0.609921</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="F24" t="n">
-        <v>0.480339</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,16 +974,16 @@
         <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.060934</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -996,104 +996,104 @@
         <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2.123375</v>
+        <v>-0.259972</v>
       </c>
       <c r="F26" t="n">
-        <v>0.799177</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.259972</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.777299</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E28" t="n">
-        <v>8.727061000000001</v>
+        <v>8.58755</v>
       </c>
       <c r="F28" t="n">
-        <v>4.223453</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>8.58755</v>
+        <v>8.825751</v>
       </c>
       <c r="F29" t="n">
-        <v>3.348378</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>8.825751</v>
+        <v>0.000557</v>
       </c>
       <c r="F30" t="n">
-        <v>3.983297</v>
+        <v>-0.000492</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>1.5</v>
+        <v>0.000557</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.25</v>
+        <v>-0.000492</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E32" t="n">
-        <v>0.000557</v>
+        <v>-0.01</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000492</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000557</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000492</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>59</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F34" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="F35" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D36" t="n">
-        <v>59</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D37" t="n">
-        <v>59</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F37" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -468,16 +468,16 @@
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>0.023687</v>
+        <v>6.25</v>
       </c>
       <c r="F2" t="n">
-        <v>0.051293</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -493,101 +493,101 @@
         <v>0.023687</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051293</v>
+        <v>0.051268</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>1.16</v>
+        <v>0.023687</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.32</v>
+        <v>0.051268</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F5" t="n">
-        <v>1.57</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2</v>
+        <v>-0.64</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>96.96513</v>
+        <v>1.2</v>
       </c>
       <c r="F7" t="n">
-        <v>109.91611</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>97.10777</v>
+        <v>96.96513</v>
       </c>
       <c r="F8" t="n">
-        <v>114.40189</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>5.4394</v>
+        <v>97.10777</v>
       </c>
       <c r="F9" t="n">
-        <v>5.2204</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4388</v>
+        <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.2126</v>
+        <v>5.2204</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4441056</v>
+        <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>7397669</v>
+        <v>5.2198</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>60</v>
       </c>
       <c r="E12" t="n">
-        <v>1894119</v>
+        <v>4441056</v>
       </c>
       <c r="F12" t="n">
-        <v>2727499</v>
+        <v>7397669</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F13" t="n">
-        <v>4670170</v>
+        <v>2727499</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F14" t="n">
-        <v>5.04</v>
+        <v>4670170</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="F15" t="n">
-        <v>3.35</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>6.03</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,16 +798,16 @@
         <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>21.42</v>
+        <v>3.01</v>
       </c>
       <c r="F17" t="n">
-        <v>32.26</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -820,38 +820,38 @@
         <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>368886</v>
+        <v>21.42</v>
       </c>
       <c r="F18" t="n">
-        <v>372616</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>0.537905</v>
+        <v>368886</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.219358</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.594556</v>
+        <v>0.537905</v>
       </c>
       <c r="F20" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>3.74306</v>
+        <v>-0.594556</v>
       </c>
       <c r="F21" t="n">
-        <v>0.748803</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>3.743473</v>
+        <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>0.609921</v>
+        <v>0.748803</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D23" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.596467</v>
+        <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>0.480339</v>
+        <v>0.7488899999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>0.888065</v>
+        <v>1.596467</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.060934</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,16 +974,16 @@
         <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>2.123375</v>
+        <v>0.888065</v>
       </c>
       <c r="F25" t="n">
-        <v>0.799177</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -996,104 +996,104 @@
         <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.259972</v>
+        <v>2.123375</v>
       </c>
       <c r="F26" t="n">
-        <v>0.777299</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>8.727061000000001</v>
+        <v>-0.259972</v>
       </c>
       <c r="F27" t="n">
-        <v>4.223453</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.58755</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>3.348378</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E29" t="n">
-        <v>8.825751</v>
+        <v>8.58755</v>
       </c>
       <c r="F29" t="n">
-        <v>3.983297</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>0.000557</v>
+        <v>8.825751</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000492</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.000557</v>
+        <v>1.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000492</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.01</v>
+        <v>0.000557</v>
       </c>
       <c r="F32" t="n">
-        <v>0.16</v>
+        <v>-0.000517</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.000557</v>
       </c>
       <c r="F33" t="n">
-        <v>0.03</v>
+        <v>-0.000517</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>59</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F34" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>59</v>
       </c>
       <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D36" t="n">
+        <v>59</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D37" t="n">
+        <v>59</v>
+      </c>
+      <c r="E37" t="n">
         <v>1.47</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,51 +543,51 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.64</v>
+        <v>1.2</v>
       </c>
       <c r="F6" t="n">
-        <v>1.57</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2</v>
+        <v>96.96513</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.32</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>96.96513</v>
+        <v>97.10777</v>
       </c>
       <c r="F8" t="n">
-        <v>109.91611</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>97.10777</v>
+        <v>5.4394</v>
       </c>
       <c r="F9" t="n">
-        <v>114.40189</v>
+        <v>5.2204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="F10" t="n">
-        <v>5.2204</v>
+        <v>5.2198</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="F11" t="n">
-        <v>5.2198</v>
+        <v>7397669</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>60</v>
       </c>
       <c r="E12" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="F12" t="n">
-        <v>7397669</v>
+        <v>2727499</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F13" t="n">
-        <v>2727499</v>
+        <v>4670170</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F14" t="n">
-        <v>4670170</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>5.04</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="F16" t="n">
-        <v>3.35</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,16 +798,16 @@
         <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="F17" t="n">
-        <v>6.03</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -820,38 +820,38 @@
         <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="F18" t="n">
-        <v>32.26</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>368886</v>
+        <v>0.537905</v>
       </c>
       <c r="F19" t="n">
-        <v>372616</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>0.537905</v>
+        <v>-0.594556</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.594556</v>
+        <v>3.74306</v>
       </c>
       <c r="F21" t="n">
-        <v>4.057001</v>
+        <v>0.748803</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="F22" t="n">
-        <v>0.748803</v>
+        <v>0.7488899999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7488899999999999</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="F24" t="n">
-        <v>0.480339</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,16 +974,16 @@
         <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.060934</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -996,38 +996,38 @@
         <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2.123375</v>
+        <v>-0.259972</v>
       </c>
       <c r="F26" t="n">
-        <v>0.799177</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.259972</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.777299</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="F28" t="n">
-        <v>4.223453</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>8.58755</v>
+        <v>1.5</v>
       </c>
       <c r="F29" t="n">
-        <v>3.348378</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>8.825751</v>
+        <v>0.000557</v>
       </c>
       <c r="F30" t="n">
-        <v>3.983297</v>
+        <v>-0.000517</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>1.5</v>
+        <v>0.000557</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.25</v>
+        <v>-0.000517</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E32" t="n">
-        <v>0.000557</v>
+        <v>-0.01</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000517</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000557</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000517</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>59</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F34" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="F35" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D36" t="n">
-        <v>59</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D37" t="n">
-        <v>59</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F37" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,16 +459,16 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D2" t="n">
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>6.25</v>
+        <v>7.75</v>
       </c>
       <c r="F2" t="n">
         <v>13.75</v>
@@ -481,19 +481,19 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>0.023687</v>
+        <v>0.024244</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051268</v>
+        <v>0.051245</v>
       </c>
     </row>
     <row r="4">
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>0.023687</v>
+        <v>0.024244</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051268</v>
+        <v>0.051245</v>
       </c>
     </row>
     <row r="5">
@@ -525,16 +525,16 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="F5" t="n">
         <v>-0.32</v>
@@ -543,660 +543,704 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D6" t="n">
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2</v>
+        <v>0.64</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D7" t="n">
         <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>96.96513</v>
+        <v>1.16</v>
       </c>
       <c r="F7" t="n">
-        <v>109.91611</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>97.10777</v>
+        <v>97.48671</v>
       </c>
       <c r="F8" t="n">
-        <v>114.40189</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>5.4394</v>
+        <v>96.53041</v>
       </c>
       <c r="F9" t="n">
-        <v>5.2204</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4388</v>
+        <v>5.643</v>
       </c>
       <c r="F10" t="n">
-        <v>5.2198</v>
+        <v>5.1809</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4441056</v>
+        <v>5.6424</v>
       </c>
       <c r="F11" t="n">
-        <v>7397669</v>
+        <v>5.2073</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1894119</v>
+        <v>4511956</v>
       </c>
       <c r="F12" t="n">
-        <v>2727499</v>
+        <v>7397669</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2546936</v>
+        <v>1910940</v>
       </c>
       <c r="F13" t="n">
-        <v>4670170</v>
+        <v>2727499</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.34</v>
+        <v>2601017</v>
       </c>
       <c r="F14" t="n">
-        <v>5.04</v>
+        <v>4670170</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="F15" t="n">
-        <v>3.35</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>6.03</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>21.42</v>
+        <v>2.99</v>
       </c>
       <c r="F17" t="n">
-        <v>32.26</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>368886</v>
+        <v>22.89</v>
       </c>
       <c r="F18" t="n">
-        <v>372616</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E19" t="n">
-        <v>0.537905</v>
+        <v>367927</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.219358</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.594556</v>
+        <v>1.608989</v>
       </c>
       <c r="F20" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>3.74306</v>
+        <v>1.36989</v>
       </c>
       <c r="F21" t="n">
-        <v>0.748803</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" t="n">
-        <v>3.743473</v>
+        <v>-0.409357</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7488899999999999</v>
+        <v>-0.013509</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D23" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.596467</v>
+        <v>-0.4094</v>
       </c>
       <c r="F23" t="n">
-        <v>0.480339</v>
+        <v>0.521205</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D24" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>0.888065</v>
+        <v>1.896096</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.060934</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.123375</v>
+        <v>1.160214</v>
       </c>
       <c r="F25" t="n">
-        <v>0.799177</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.259972</v>
+        <v>2.436662</v>
       </c>
       <c r="F26" t="n">
-        <v>0.777299</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44804</v>
+        <v>44530</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E27" t="n">
-        <v>8.727061000000001</v>
+        <v>-0.042128</v>
       </c>
       <c r="F27" t="n">
-        <v>4.223453</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E28" t="n">
-        <v>8.825751</v>
+        <v>7.168596</v>
       </c>
       <c r="F28" t="n">
-        <v>3.983297</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44500</v>
+        <v>44834</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.25</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44500</v>
+        <v>44834</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E30" t="n">
-        <v>0.000557</v>
+        <v>7.191214</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000517</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D31" t="n">
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.000557</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000517</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
         <v>59</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.01</v>
+        <v>0.005012</v>
       </c>
       <c r="F32" t="n">
-        <v>0.16</v>
+        <v>-0.00054</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D33" t="n">
         <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.005012</v>
       </c>
       <c r="F33" t="n">
-        <v>0.03</v>
+        <v>-0.00054</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D34" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F34" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D35" t="n">
+        <v>58</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>dif_juros_credito_total</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D35" t="n">
-        <v>59</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F35" t="n">
+      <c r="B37" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="F37" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,16 +484,16 @@
         <v>44500</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.024244</v>
+        <v>0.024273</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051245</v>
+        <v>0.050788</v>
       </c>
     </row>
     <row r="4">
@@ -506,16 +506,16 @@
         <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.024244</v>
+        <v>0.024273</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051245</v>
+        <v>0.050788</v>
       </c>
     </row>
     <row r="5">
@@ -638,16 +638,16 @@
         <v>44500</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" t="n">
         <v>5.643</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1809</v>
+        <v>5.2079</v>
       </c>
     </row>
     <row r="11">
@@ -675,7 +675,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="F12" t="n">
-        <v>7397669</v>
+        <v>2727499</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="F13" t="n">
-        <v>2727499</v>
+        <v>4670170</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="F14" t="n">
-        <v>4670170</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>5.04</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="F16" t="n">
-        <v>3.35</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,148 +798,148 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>2.99</v>
+        <v>367927</v>
       </c>
       <c r="F17" t="n">
-        <v>6.03</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E18" t="n">
-        <v>22.89</v>
+        <v>1.608989</v>
       </c>
       <c r="F18" t="n">
-        <v>32.26</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>367927</v>
+        <v>1.36989</v>
       </c>
       <c r="F19" t="n">
-        <v>372616</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E20" t="n">
-        <v>1.608989</v>
+        <v>-0.409357</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.219358</v>
+        <v>0.521145</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>1.36989</v>
+        <v>-0.4094</v>
       </c>
       <c r="F21" t="n">
-        <v>4.057001</v>
+        <v>0.521205</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D22" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.409357</v>
+        <v>1.160214</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.013509</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4094</v>
+        <v>2.436662</v>
       </c>
       <c r="F23" t="n">
-        <v>0.521205</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,296 +952,208 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.896096</v>
+        <v>-0.042128</v>
       </c>
       <c r="F24" t="n">
-        <v>0.480339</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E25" t="n">
-        <v>1.160214</v>
+        <v>7.168596</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.060934</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E26" t="n">
-        <v>2.436662</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.799177</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.042128</v>
+        <v>7.191214</v>
       </c>
       <c r="F27" t="n">
-        <v>0.777299</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D28" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E28" t="n">
-        <v>7.168596</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>4.223453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>8.248760000000001</v>
+        <v>0.004983</v>
       </c>
       <c r="F29" t="n">
-        <v>3.348378</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>7.191214</v>
+        <v>0.004983</v>
       </c>
       <c r="F30" t="n">
-        <v>3.983297</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.00054</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.005012</v>
+        <v>0.02</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.00054</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_total</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D34" t="n">
-        <v>58</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D35" t="n">
-        <v>58</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F36" t="n">
         <v>0.23</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,95 +499,95 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" t="n">
-        <v>0.024273</v>
+        <v>1.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.050788</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F6" t="n">
-        <v>1.57</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" t="n">
-        <v>1.16</v>
+        <v>97.48671</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.32</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>97.48671</v>
+        <v>96.53041</v>
       </c>
       <c r="F8" t="n">
-        <v>109.91611</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>96.53041</v>
+        <v>5.643</v>
       </c>
       <c r="F9" t="n">
-        <v>114.40189</v>
+        <v>5.2079</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,32 +644,32 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.643</v>
+        <v>5.6424</v>
       </c>
       <c r="F10" t="n">
-        <v>5.2079</v>
+        <v>5.2073</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="F11" t="n">
-        <v>5.2073</v>
+        <v>7397669</v>
       </c>
     </row>
     <row r="12">
@@ -785,7 +785,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,38 +798,38 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>367927</v>
+        <v>22.89</v>
       </c>
       <c r="F17" t="n">
-        <v>372616</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>1.608989</v>
+        <v>367927</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.219358</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
@@ -842,38 +842,38 @@
         <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>1.36989</v>
+        <v>1.608989</v>
       </c>
       <c r="F19" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D20" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.409357</v>
+        <v>1.36989</v>
       </c>
       <c r="F20" t="n">
-        <v>0.521145</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
@@ -886,38 +886,38 @@
         <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4094</v>
+        <v>-0.409357</v>
       </c>
       <c r="F21" t="n">
-        <v>0.521205</v>
+        <v>0.521145</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>1.160214</v>
+        <v>-0.4094</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.060934</v>
+        <v>0.521205</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
@@ -930,16 +930,16 @@
         <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>2.436662</v>
+        <v>1.896096</v>
       </c>
       <c r="F23" t="n">
-        <v>0.799177</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,60 +952,60 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.042128</v>
+        <v>1.160214</v>
       </c>
       <c r="F24" t="n">
-        <v>0.777299</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>7.168596</v>
+        <v>2.436662</v>
       </c>
       <c r="F25" t="n">
-        <v>4.223453</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>8.248760000000001</v>
+        <v>-0.042128</v>
       </c>
       <c r="F26" t="n">
-        <v>3.348378</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
@@ -1018,60 +1018,60 @@
         <v>48</v>
       </c>
       <c r="E27" t="n">
-        <v>7.191214</v>
+        <v>7.168596</v>
       </c>
       <c r="F27" t="n">
-        <v>3.983297</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E29" t="n">
-        <v>0.004983</v>
+        <v>7.191214</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.000457</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
@@ -1084,38 +1084,38 @@
         <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>0.004983</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D31" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.03</v>
+        <v>0.004983</v>
       </c>
       <c r="F31" t="n">
-        <v>0.16</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1131,13 +1131,13 @@
         <v>0.03</v>
       </c>
       <c r="F32" t="n">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1150,10 +1150,54 @@
         <v>58</v>
       </c>
       <c r="E33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D34" t="n">
+        <v>58</v>
+      </c>
+      <c r="E34" t="n">
         <v>0.02</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F34" t="n">
         <v>0.23</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D35" t="n">
+        <v>58</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -468,192 +468,192 @@
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>7.75</v>
+        <v>0.024306</v>
       </c>
       <c r="F2" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E3" t="n">
-        <v>0.024273</v>
+        <v>1.25</v>
       </c>
       <c r="F3" t="n">
-        <v>0.050788</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F5" t="n">
-        <v>1.57</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6" t="n">
-        <v>1.16</v>
+        <v>96.53041</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.32</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D7" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
-        <v>97.48671</v>
+        <v>5.643</v>
       </c>
       <c r="F7" t="n">
-        <v>109.91611</v>
+        <v>4.9859</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D8" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>96.53041</v>
+        <v>5.6424</v>
       </c>
       <c r="F8" t="n">
-        <v>114.40189</v>
+        <v>4.9853</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>5.643</v>
+        <v>1910940</v>
       </c>
       <c r="F9" t="n">
-        <v>5.2079</v>
+        <v>2727499</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E10" t="n">
-        <v>5.6424</v>
+        <v>2.33</v>
       </c>
       <c r="F10" t="n">
-        <v>5.2073</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -666,16 +666,16 @@
         <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>4511956</v>
+        <v>1.43</v>
       </c>
       <c r="F11" t="n">
-        <v>7397669</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1910940</v>
+        <v>2.99</v>
       </c>
       <c r="F12" t="n">
-        <v>2727499</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2601017</v>
+        <v>22.89</v>
       </c>
       <c r="F13" t="n">
-        <v>4670170</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,214 +732,214 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.33</v>
+        <v>367927</v>
       </c>
       <c r="F14" t="n">
-        <v>5.04</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>1.36989</v>
       </c>
       <c r="F15" t="n">
-        <v>3.35</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>2.99</v>
+        <v>-0.409357</v>
       </c>
       <c r="F16" t="n">
-        <v>6.03</v>
+        <v>-3.763825</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>22.89</v>
+        <v>-0.4094</v>
       </c>
       <c r="F17" t="n">
-        <v>32.26</v>
+        <v>-3.764261</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" t="n">
-        <v>367927</v>
+        <v>1.160214</v>
       </c>
       <c r="F18" t="n">
-        <v>372616</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>1.608989</v>
+        <v>-0.042128</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.219358</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E20" t="n">
-        <v>1.36989</v>
+        <v>7.168596</v>
       </c>
       <c r="F20" t="n">
-        <v>4.057001</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.409357</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.521145</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4094</v>
+        <v>7.191214</v>
       </c>
       <c r="F22" t="n">
-        <v>0.521205</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.896096</v>
+        <v>0.00495</v>
       </c>
       <c r="F23" t="n">
-        <v>0.480339</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.160214</v>
+        <v>0.03</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.060934</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,16 +974,16 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.436662</v>
+        <v>0.03</v>
       </c>
       <c r="F25" t="n">
-        <v>0.799177</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -996,207 +996,31 @@
         <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.042128</v>
+        <v>0.02</v>
       </c>
       <c r="F26" t="n">
-        <v>0.777299</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E27" t="n">
-        <v>7.168596</v>
+        <v>1.02</v>
       </c>
       <c r="F27" t="n">
-        <v>4.223453</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>igp_m_acum_12m</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>44834</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D28" t="n">
-        <v>49</v>
-      </c>
-      <c r="E28" t="n">
-        <v>8.248760000000001</v>
-      </c>
-      <c r="F28" t="n">
-        <v>3.348378</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>inpc_acum_12m</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="n">
-        <v>44834</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D29" t="n">
-        <v>48</v>
-      </c>
-      <c r="E29" t="n">
-        <v>7.191214</v>
-      </c>
-      <c r="F29" t="n">
-        <v>3.983297</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>dif_selic_meta</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>46326</v>
-      </c>
-      <c r="D30" t="n">
-        <v>60</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>dif_selic_over</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>46326</v>
-      </c>
-      <c r="D31" t="n">
-        <v>60</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.004983</v>
-      </c>
-      <c r="F31" t="n">
-        <v>-0.000457</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_total</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D32" t="n">
-        <v>58</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D33" t="n">
-        <v>58</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D34" t="n">
-        <v>58</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D35" t="n">
-        <v>58</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="F35" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -468,60 +468,60 @@
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>0.024306</v>
+        <v>7.75</v>
       </c>
       <c r="F2" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>1.25</v>
+        <v>0.024342</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.32</v>
+        <v>0.050788</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.64</v>
+        <v>0.024342</v>
       </c>
       <c r="F4" t="n">
-        <v>1.57</v>
+        <v>0.050788</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,7 +534,7 @@
         <v>59</v>
       </c>
       <c r="E5" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="F5" t="n">
         <v>-0.32</v>
@@ -543,117 +543,117 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>96.53041</v>
+        <v>0.64</v>
       </c>
       <c r="F6" t="n">
-        <v>114.40189</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E7" t="n">
-        <v>5.643</v>
+        <v>97.48671</v>
       </c>
       <c r="F7" t="n">
-        <v>4.9859</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>5.6424</v>
+        <v>96.53041</v>
       </c>
       <c r="F8" t="n">
-        <v>4.9853</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>1910940</v>
+        <v>5.643</v>
       </c>
       <c r="F9" t="n">
-        <v>2727499</v>
+        <v>4.9698</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>2.33</v>
+        <v>5.6424</v>
       </c>
       <c r="F10" t="n">
-        <v>5.04</v>
+        <v>4.9853</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -666,16 +666,16 @@
         <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>1.43</v>
+        <v>4511956</v>
       </c>
       <c r="F11" t="n">
-        <v>3.35</v>
+        <v>7397669</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>2.99</v>
+        <v>1910940</v>
       </c>
       <c r="F12" t="n">
-        <v>6.03</v>
+        <v>2727499</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>22.89</v>
+        <v>2601017</v>
       </c>
       <c r="F13" t="n">
-        <v>32.26</v>
+        <v>4670170</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,214 +732,214 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>367927</v>
+        <v>2.33</v>
       </c>
       <c r="F14" t="n">
-        <v>372616</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.36989</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>4.057001</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.409357</v>
+        <v>2.99</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.763825</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4094</v>
+        <v>22.89</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.764261</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>1.160214</v>
+        <v>367927</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.060934</v>
+        <v>372616</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.042128</v>
+        <v>1.608989</v>
       </c>
       <c r="F19" t="n">
-        <v>0.777299</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>7.168596</v>
+        <v>1.36989</v>
       </c>
       <c r="F20" t="n">
-        <v>4.223453</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D21" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>8.248760000000001</v>
+        <v>-0.409357</v>
       </c>
       <c r="F21" t="n">
-        <v>3.348378</v>
+        <v>-4.074582</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D22" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>7.191214</v>
+        <v>-0.4094</v>
       </c>
       <c r="F22" t="n">
-        <v>3.983297</v>
+        <v>-3.764261</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00495</v>
+        <v>1.896096</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.000457</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03</v>
+        <v>1.160214</v>
       </c>
       <c r="F24" t="n">
-        <v>0.16</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,16 +974,16 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03</v>
+        <v>2.436662</v>
       </c>
       <c r="F25" t="n">
-        <v>0.03</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -996,31 +996,207 @@
         <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02</v>
+        <v>-0.042128</v>
       </c>
       <c r="F26" t="n">
-        <v>0.23</v>
+        <v>0.777299</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>ipca_acum_12m</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>44834</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D27" t="n">
+        <v>48</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7.168596</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.223453</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>igp_m_acum_12m</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>44834</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D28" t="n">
+        <v>49</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8.248760000000001</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.348378</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>dif_selic_meta</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="D29" t="n">
+        <v>60</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>dif_selic_over</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="D30" t="n">
+        <v>60</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.004914</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.000457</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>dif_cdi</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="D31" t="n">
+        <v>60</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.004914</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.000457</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_total</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D32" t="n">
+        <v>58</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D33" t="n">
+        <v>58</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D34" t="n">
+        <v>58</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>dif_juros_credito_total</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D27" t="n">
+      <c r="B35" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D35" t="n">
         <v>58</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E35" t="n">
         <v>1.02</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F35" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -455,7 +455,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -468,16 +468,16 @@
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>7.75</v>
+        <v>0.024383</v>
       </c>
       <c r="F2" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.024342</v>
+        <v>0.024383</v>
       </c>
       <c r="F3" t="n">
         <v>0.050788</v>
@@ -499,67 +499,67 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" t="n">
-        <v>0.024342</v>
+        <v>1.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.050788</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F6" t="n">
-        <v>1.57</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="7">
@@ -625,7 +625,7 @@
         <v>5.643</v>
       </c>
       <c r="F9" t="n">
-        <v>4.9698</v>
+        <v>4.9935</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>5.6424</v>
       </c>
       <c r="F10" t="n">
-        <v>4.9853</v>
+        <v>4.9929</v>
       </c>
     </row>
     <row r="11">
@@ -889,7 +889,7 @@
         <v>-0.409357</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.074582</v>
+        <v>-3.617132</v>
       </c>
     </row>
     <row r="22">
@@ -911,7 +911,7 @@
         <v>-0.4094</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.764261</v>
+        <v>-3.617551</v>
       </c>
     </row>
     <row r="23">
@@ -1049,23 +1049,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>7.191214</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="30">
@@ -1084,7 +1084,7 @@
         <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>0.004914</v>
+        <v>0.004873</v>
       </c>
       <c r="F30" t="n">
         <v>-0.000457</v>
@@ -1106,7 +1106,7 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004914</v>
+        <v>0.004873</v>
       </c>
       <c r="F31" t="n">
         <v>-0.000457</v>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -468,16 +468,16 @@
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>0.024383</v>
+        <v>7.75</v>
       </c>
       <c r="F2" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.024383</v>
+        <v>0.02443</v>
       </c>
       <c r="F3" t="n">
         <v>0.050788</v>
@@ -499,95 +499,95 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>1.25</v>
+        <v>0.02443</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.32</v>
+        <v>0.050788</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="n">
-        <v>0.64</v>
+        <v>1.25</v>
       </c>
       <c r="F5" t="n">
-        <v>1.57</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>1.16</v>
+        <v>0.64</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>97.48671</v>
+        <v>1.16</v>
       </c>
       <c r="F7" t="n">
-        <v>109.91611</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>96.53041</v>
+        <v>97.48671</v>
       </c>
       <c r="F8" t="n">
-        <v>114.40189</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>5.643</v>
+        <v>96.53041</v>
       </c>
       <c r="F9" t="n">
-        <v>4.9935</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.6424</v>
+        <v>5.643</v>
       </c>
       <c r="F10" t="n">
-        <v>4.9929</v>
+        <v>5.0119</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4511956</v>
+        <v>5.6424</v>
       </c>
       <c r="F11" t="n">
-        <v>7397669</v>
+        <v>5.0113</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1910940</v>
+        <v>4511956</v>
       </c>
       <c r="F12" t="n">
-        <v>2727499</v>
+        <v>7397669</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2601017</v>
+        <v>1910940</v>
       </c>
       <c r="F13" t="n">
-        <v>4670170</v>
+        <v>2727499</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.33</v>
+        <v>2601017</v>
       </c>
       <c r="F14" t="n">
-        <v>5.04</v>
+        <v>4670170</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="F15" t="n">
-        <v>3.35</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>2.99</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>6.03</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,16 +798,16 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>22.89</v>
+        <v>2.99</v>
       </c>
       <c r="F17" t="n">
-        <v>32.26</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -820,38 +820,38 @@
         <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>367927</v>
+        <v>22.89</v>
       </c>
       <c r="F18" t="n">
-        <v>372616</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>1.608989</v>
+        <v>367927</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.219358</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>1.36989</v>
+        <v>1.608989</v>
       </c>
       <c r="F20" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.409357</v>
+        <v>1.36989</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.617132</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4094</v>
+        <v>-0.409357</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.617551</v>
+        <v>-3.261982</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.896096</v>
+        <v>-0.4094</v>
       </c>
       <c r="F23" t="n">
-        <v>0.480339</v>
+        <v>-3.262359</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.160214</v>
+        <v>1.896096</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.060934</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,16 +974,16 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.436662</v>
+        <v>1.160214</v>
       </c>
       <c r="F25" t="n">
-        <v>0.799177</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -996,104 +996,104 @@
         <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.042128</v>
+        <v>2.436662</v>
       </c>
       <c r="F26" t="n">
-        <v>0.777299</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D27" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>7.168596</v>
+        <v>-0.042128</v>
       </c>
       <c r="F27" t="n">
-        <v>4.223453</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E28" t="n">
-        <v>8.248760000000001</v>
+        <v>7.168596</v>
       </c>
       <c r="F28" t="n">
-        <v>3.348378</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D29" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>7.191214</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>3.983297</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E30" t="n">
-        <v>0.004873</v>
+        <v>7.191214</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000457</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004873</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.03</v>
+        <v>0.004826</v>
       </c>
       <c r="F32" t="n">
-        <v>0.16</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03</v>
+        <v>0.004826</v>
       </c>
       <c r="F33" t="n">
-        <v>0.03</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F34" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>1.02</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,95 +499,95 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02443</v>
+        <v>1.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.050788</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F6" t="n">
-        <v>1.57</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" t="n">
-        <v>1.16</v>
+        <v>97.48671</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.32</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>97.48671</v>
+        <v>96.53041</v>
       </c>
       <c r="F8" t="n">
-        <v>109.91611</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>96.53041</v>
+        <v>5.643</v>
       </c>
       <c r="F9" t="n">
-        <v>114.40189</v>
+        <v>5.0119</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.643</v>
+        <v>5.6424</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0119</v>
+        <v>5.0113</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0113</v>
+        <v>7397669</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="F12" t="n">
-        <v>7397669</v>
+        <v>2727499</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="F13" t="n">
-        <v>2727499</v>
+        <v>4670170</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="F14" t="n">
-        <v>4670170</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>5.04</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="F16" t="n">
-        <v>3.35</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="F17" t="n">
-        <v>6.03</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="F18" t="n">
-        <v>32.26</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>367927</v>
+        <v>1.608989</v>
       </c>
       <c r="F19" t="n">
-        <v>362821</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>1.608989</v>
+        <v>1.36989</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>1.36989</v>
+        <v>-0.409357</v>
       </c>
       <c r="F21" t="n">
-        <v>4.057001</v>
+        <v>-3.261982</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.409357</v>
+        <v>-0.4094</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.261982</v>
+        <v>-3.262359</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4094</v>
+        <v>1.896096</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.262359</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.896096</v>
+        <v>1.160214</v>
       </c>
       <c r="F24" t="n">
-        <v>0.480339</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,126 +974,126 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>1.160214</v>
+        <v>2.436662</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.060934</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2.436662</v>
+        <v>-0.042128</v>
       </c>
       <c r="F26" t="n">
-        <v>0.799177</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.042128</v>
+        <v>7.168596</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.628712</v>
+        <v>4.223453</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D28" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>7.168596</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>4.223453</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E29" t="n">
-        <v>8.248760000000001</v>
+        <v>7.191214</v>
       </c>
       <c r="F29" t="n">
-        <v>3.348378</v>
+        <v>3.983297</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>7.191214</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>3.983297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.004826</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.004826</v>
+        <v>0.03</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000457</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.004826</v>
+        <v>0.03</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000457</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F34" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>0.03</v>
+        <v>1.02</v>
       </c>
       <c r="F35" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="F37" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02443</v>
+        <v>0.024483</v>
       </c>
       <c r="F3" t="n">
         <v>0.050788</v>
@@ -499,29 +499,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>1.25</v>
+        <v>0.024483</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.32</v>
+        <v>0.050788</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,60 +534,60 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>0.64</v>
+        <v>1.25</v>
       </c>
       <c r="F5" t="n">
-        <v>1.57</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>1.16</v>
+        <v>0.64</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.32</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>97.48671</v>
+        <v>1.16</v>
       </c>
       <c r="F7" t="n">
-        <v>109.91611</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>96.53041</v>
+        <v>97.48671</v>
       </c>
       <c r="F8" t="n">
-        <v>114.40189</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>5.643</v>
+        <v>96.53041</v>
       </c>
       <c r="F9" t="n">
-        <v>5.0119</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.6424</v>
+        <v>5.643</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0113</v>
+        <v>4.9892</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4511956</v>
+        <v>5.6424</v>
       </c>
       <c r="F11" t="n">
-        <v>7397669</v>
+        <v>4.9886</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1910940</v>
+        <v>4511956</v>
       </c>
       <c r="F12" t="n">
-        <v>2727499</v>
+        <v>7397669</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2601017</v>
+        <v>1910940</v>
       </c>
       <c r="F13" t="n">
-        <v>4670170</v>
+        <v>2727499</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.33</v>
+        <v>2601017</v>
       </c>
       <c r="F14" t="n">
-        <v>5.04</v>
+        <v>4670170</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="F15" t="n">
-        <v>3.35</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>2.99</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>6.03</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,32 +798,32 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>22.89</v>
+        <v>2.99</v>
       </c>
       <c r="F17" t="n">
-        <v>32.26</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>367927</v>
+        <v>22.89</v>
       </c>
       <c r="F18" t="n">
-        <v>362821</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="19">
@@ -889,7 +889,7 @@
         <v>-0.409357</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.261982</v>
+        <v>-3.700129</v>
       </c>
     </row>
     <row r="22">
@@ -911,7 +911,7 @@
         <v>-0.4094</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.262359</v>
+        <v>-3.700558</v>
       </c>
     </row>
     <row r="23">
@@ -983,51 +983,51 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.042128</v>
+        <v>7.168596</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.628712</v>
+        <v>4.57612</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D27" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>7.168596</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>4.223453</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,38 +1040,38 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.248760000000001</v>
+        <v>7.191214</v>
       </c>
       <c r="F28" t="n">
-        <v>3.348378</v>
+        <v>4.293633</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D29" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>7.191214</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>3.983297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
@@ -1084,16 +1084,16 @@
         <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.004773</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,7 +1106,7 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004826</v>
+        <v>0.004773</v>
       </c>
       <c r="F31" t="n">
         <v>-0.000457</v>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -829,29 +829,29 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>1.608989</v>
+        <v>367927</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.219358</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>1.36989</v>
+        <v>1.608989</v>
       </c>
       <c r="F20" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.409357</v>
+        <v>1.36989</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.700129</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4094</v>
+        <v>-0.409357</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.700558</v>
+        <v>-3.700129</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.896096</v>
+        <v>-0.4094</v>
       </c>
       <c r="F23" t="n">
-        <v>0.480339</v>
+        <v>-3.700558</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.160214</v>
+        <v>1.896096</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.060934</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.436662</v>
+        <v>1.160214</v>
       </c>
       <c r="F25" t="n">
-        <v>0.799177</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>7.168596</v>
+        <v>2.436662</v>
       </c>
       <c r="F26" t="n">
-        <v>4.57612</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>8.248760000000001</v>
+        <v>-0.042128</v>
       </c>
       <c r="F27" t="n">
-        <v>3.348378</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>7.191214</v>
+        <v>7.168596</v>
       </c>
       <c r="F28" t="n">
-        <v>4.293633</v>
+        <v>4.57612</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>0.004773</v>
+        <v>7.191214</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000457</v>
+        <v>4.293633</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004773</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.03</v>
+        <v>0.004773</v>
       </c>
       <c r="F32" t="n">
-        <v>0.16</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03</v>
+        <v>0.004773</v>
       </c>
       <c r="F33" t="n">
-        <v>0.03</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F34" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>1.02</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,7 +763,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="F16" t="n">
-        <v>3.35</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="F17" t="n">
-        <v>6.03</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="F18" t="n">
-        <v>32.26</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>367927</v>
+        <v>1.608989</v>
       </c>
       <c r="F19" t="n">
-        <v>362821</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>1.608989</v>
+        <v>1.36989</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>1.36989</v>
+        <v>-0.409357</v>
       </c>
       <c r="F21" t="n">
-        <v>4.057001</v>
+        <v>-3.700129</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.409357</v>
+        <v>-0.4094</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.700129</v>
+        <v>-3.700558</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4094</v>
+        <v>1.896096</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.700558</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.896096</v>
+        <v>1.160214</v>
       </c>
       <c r="F24" t="n">
-        <v>0.480339</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>1.160214</v>
+        <v>2.436662</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.060934</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2.436662</v>
+        <v>-0.042128</v>
       </c>
       <c r="F26" t="n">
-        <v>0.799177</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.042128</v>
+        <v>7.168596</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.628712</v>
+        <v>4.57612</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,16 +1040,16 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>7.168596</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>4.57612</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,38 +1062,38 @@
         <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>8.248760000000001</v>
+        <v>7.191214</v>
       </c>
       <c r="F29" t="n">
-        <v>3.348378</v>
+        <v>4.293633</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>7.191214</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>4.293633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,16 +1106,16 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.004773</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1137,29 +1137,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.004773</v>
+        <v>0.03</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000457</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F34" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>0.03</v>
+        <v>1.02</v>
       </c>
       <c r="F35" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="F37" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,7 +763,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>2.99</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>6.03</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>22.89</v>
+        <v>2.99</v>
       </c>
       <c r="F17" t="n">
-        <v>32.26</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>367927</v>
+        <v>22.89</v>
       </c>
       <c r="F18" t="n">
-        <v>362821</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>1.608989</v>
+        <v>367927</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.219358</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>1.36989</v>
+        <v>1.608989</v>
       </c>
       <c r="F20" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.409357</v>
+        <v>1.36989</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.700129</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4094</v>
+        <v>-0.409357</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.700558</v>
+        <v>-3.700129</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.896096</v>
+        <v>-0.4094</v>
       </c>
       <c r="F23" t="n">
-        <v>0.480339</v>
+        <v>-3.700558</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.160214</v>
+        <v>1.896096</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.060934</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.436662</v>
+        <v>1.160214</v>
       </c>
       <c r="F25" t="n">
-        <v>0.799177</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.042128</v>
+        <v>2.436662</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.628712</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>7.168596</v>
+        <v>-0.042128</v>
       </c>
       <c r="F27" t="n">
-        <v>4.57612</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,16 +1040,16 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.248760000000001</v>
+        <v>7.168596</v>
       </c>
       <c r="F28" t="n">
-        <v>3.348378</v>
+        <v>4.57612</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,38 +1062,38 @@
         <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>7.191214</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>4.293633</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>7.191214</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>4.293633</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,16 +1106,16 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004773</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1137,29 +1137,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03</v>
+        <v>0.004773</v>
       </c>
       <c r="F33" t="n">
-        <v>0.16</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F34" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>1.02</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.024483</v>
+        <v>0.024544</v>
       </c>
       <c r="F3" t="n">
         <v>0.050788</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.024483</v>
+        <v>0.024544</v>
       </c>
       <c r="F4" t="n">
         <v>0.050788</v>
@@ -1128,7 +1128,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.004773</v>
+        <v>0.004712</v>
       </c>
       <c r="F32" t="n">
         <v>-0.000457</v>
@@ -1150,7 +1150,7 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.004773</v>
+        <v>0.004712</v>
       </c>
       <c r="F33" t="n">
         <v>-0.000457</v>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,29 +499,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>0.024544</v>
+        <v>1.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.050788</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,16 +534,16 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="F5" t="n">
-        <v>0.82</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -556,38 +556,38 @@
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F6" t="n">
-        <v>1.57</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E7" t="n">
-        <v>1.16</v>
+        <v>97.48671</v>
       </c>
       <c r="F7" t="n">
-        <v>0.82</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>97.48671</v>
+        <v>96.53041</v>
       </c>
       <c r="F8" t="n">
-        <v>109.91611</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>96.53041</v>
+        <v>5.643</v>
       </c>
       <c r="F9" t="n">
-        <v>114.40189</v>
+        <v>5.0096</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.643</v>
+        <v>5.6424</v>
       </c>
       <c r="F10" t="n">
-        <v>4.9892</v>
+        <v>5.009</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="F11" t="n">
-        <v>4.9886</v>
+        <v>7397669</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="F12" t="n">
-        <v>7397669</v>
+        <v>2727499</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="F13" t="n">
-        <v>2727499</v>
+        <v>4670170</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="F14" t="n">
-        <v>4670170</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>5.04</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="F16" t="n">
-        <v>3.35</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="F17" t="n">
-        <v>6.03</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="F18" t="n">
-        <v>32.26</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>367927</v>
+        <v>1.608989</v>
       </c>
       <c r="F19" t="n">
-        <v>362821</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>1.608989</v>
+        <v>1.36989</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.219358</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>1.36989</v>
+        <v>-0.409357</v>
       </c>
       <c r="F21" t="n">
-        <v>4.057001</v>
+        <v>-3.306375</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.409357</v>
+        <v>-0.4094</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.700129</v>
+        <v>-3.306758</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4094</v>
+        <v>1.896096</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.700558</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.896096</v>
+        <v>1.160214</v>
       </c>
       <c r="F24" t="n">
-        <v>0.480339</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>1.160214</v>
+        <v>2.436662</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.060934</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2.436662</v>
+        <v>-0.042128</v>
       </c>
       <c r="F26" t="n">
-        <v>0.799177</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.042128</v>
+        <v>7.168596</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.628712</v>
+        <v>4.57612</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,16 +1040,16 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>7.168596</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>4.57612</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,38 +1062,38 @@
         <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>8.248760000000001</v>
+        <v>7.191214</v>
       </c>
       <c r="F29" t="n">
-        <v>3.348378</v>
+        <v>4.293633</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>7.191214</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>4.293633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.004712</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.004712</v>
+        <v>0.03</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000457</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.004712</v>
+        <v>0.03</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000457</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F34" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>0.03</v>
+        <v>1.02</v>
       </c>
       <c r="F35" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="F37" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.024544</v>
+        <v>0.024615</v>
       </c>
       <c r="F3" t="n">
         <v>0.050788</v>
@@ -499,29 +499,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>1.25</v>
+        <v>0.024615</v>
       </c>
       <c r="F4" t="n">
-        <v>0.82</v>
+        <v>0.050788</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,16 +534,16 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>0.64</v>
+        <v>1.25</v>
       </c>
       <c r="F5" t="n">
-        <v>1.57</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -556,38 +556,38 @@
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>1.16</v>
+        <v>0.64</v>
       </c>
       <c r="F6" t="n">
-        <v>0.82</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>97.48671</v>
+        <v>1.16</v>
       </c>
       <c r="F7" t="n">
-        <v>109.91611</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>96.53041</v>
+        <v>97.48671</v>
       </c>
       <c r="F8" t="n">
-        <v>114.40189</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>5.643</v>
+        <v>96.53041</v>
       </c>
       <c r="F9" t="n">
-        <v>5.0096</v>
+        <v>114.40189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.6424</v>
+        <v>5.643</v>
       </c>
       <c r="F10" t="n">
-        <v>5.009</v>
+        <v>5.0096</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4511956</v>
+        <v>5.6424</v>
       </c>
       <c r="F11" t="n">
-        <v>7397669</v>
+        <v>5.009</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1910940</v>
+        <v>4511956</v>
       </c>
       <c r="F12" t="n">
-        <v>2727499</v>
+        <v>7397669</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2601017</v>
+        <v>1910940</v>
       </c>
       <c r="F13" t="n">
-        <v>4670170</v>
+        <v>2727499</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.33</v>
+        <v>2601017</v>
       </c>
       <c r="F14" t="n">
-        <v>5.04</v>
+        <v>4670170</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="F15" t="n">
-        <v>3.35</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>2.99</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>6.03</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>22.89</v>
+        <v>2.99</v>
       </c>
       <c r="F17" t="n">
-        <v>32.26</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>367927</v>
+        <v>22.89</v>
       </c>
       <c r="F18" t="n">
-        <v>362821</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>1.608989</v>
+        <v>367927</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.219358</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>1.36989</v>
+        <v>1.608989</v>
       </c>
       <c r="F20" t="n">
-        <v>4.057001</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46326</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.409357</v>
+        <v>1.36989</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.306375</v>
+        <v>4.057001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4094</v>
+        <v>-0.409357</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.306758</v>
+        <v>-3.306375</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.896096</v>
+        <v>-0.4094</v>
       </c>
       <c r="F23" t="n">
-        <v>0.480339</v>
+        <v>-3.306758</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.160214</v>
+        <v>1.896096</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.060934</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.436662</v>
+        <v>1.160214</v>
       </c>
       <c r="F25" t="n">
-        <v>0.799177</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.042128</v>
+        <v>2.436662</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.628712</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>7.168596</v>
+        <v>-0.042128</v>
       </c>
       <c r="F27" t="n">
-        <v>4.57612</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,16 +1040,16 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.248760000000001</v>
+        <v>7.168596</v>
       </c>
       <c r="F28" t="n">
-        <v>3.348378</v>
+        <v>4.57612</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,38 +1062,38 @@
         <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>7.191214</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>4.293633</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>7.191214</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>4.293633</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004712</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.03</v>
+        <v>0.004641</v>
       </c>
       <c r="F32" t="n">
-        <v>0.16</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03</v>
+        <v>0.004641</v>
       </c>
       <c r="F33" t="n">
-        <v>0.03</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F34" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>1.02</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,51 +477,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>0.024615</v>
+        <v>1.25</v>
       </c>
       <c r="F3" t="n">
-        <v>0.050788</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>0.024615</v>
+        <v>0.64</v>
       </c>
       <c r="F4" t="n">
-        <v>0.050788</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,7 +534,7 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="F5" t="n">
         <v>0.82</v>
@@ -543,139 +543,139 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E6" t="n">
-        <v>0.64</v>
+        <v>97.48671</v>
       </c>
       <c r="F6" t="n">
-        <v>1.57</v>
+        <v>109.91611</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
-        <v>1.16</v>
+        <v>5.6424</v>
       </c>
       <c r="F7" t="n">
-        <v>0.82</v>
+        <v>5.0435</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>97.48671</v>
+        <v>4511956</v>
       </c>
       <c r="F8" t="n">
-        <v>109.91611</v>
+        <v>7397669</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>96.53041</v>
+        <v>2601017</v>
       </c>
       <c r="F9" t="n">
-        <v>114.40189</v>
+        <v>4670170</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E10" t="n">
-        <v>5.643</v>
+        <v>2.33</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0096</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.6424</v>
+        <v>1.43</v>
       </c>
       <c r="F11" t="n">
-        <v>5.009</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4511956</v>
+        <v>2.99</v>
       </c>
       <c r="F12" t="n">
-        <v>7397669</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,214 +710,214 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1910940</v>
+        <v>22.89</v>
       </c>
       <c r="F13" t="n">
-        <v>2727499</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>2601017</v>
+        <v>367927</v>
       </c>
       <c r="F14" t="n">
-        <v>4670170</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>2.33</v>
+        <v>1.608989</v>
       </c>
       <c r="F15" t="n">
-        <v>5.04</v>
+        <v>-0.219358</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>-0.4094</v>
       </c>
       <c r="F16" t="n">
-        <v>3.35</v>
+        <v>-2.640774</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" t="n">
-        <v>2.99</v>
+        <v>1.896096</v>
       </c>
       <c r="F17" t="n">
-        <v>6.03</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" t="n">
-        <v>22.89</v>
+        <v>2.436662</v>
       </c>
       <c r="F18" t="n">
-        <v>32.26</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" t="n">
-        <v>367927</v>
+        <v>-0.042128</v>
       </c>
       <c r="F19" t="n">
-        <v>362821</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E20" t="n">
-        <v>1.608989</v>
+        <v>7.168596</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.219358</v>
+        <v>4.57612</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E21" t="n">
-        <v>1.36989</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>4.057001</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.409357</v>
+        <v>7.191214</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.306375</v>
+        <v>4.293633</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
@@ -930,16 +930,16 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4094</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.306758</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.896096</v>
+        <v>0.03</v>
       </c>
       <c r="F24" t="n">
-        <v>0.480339</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,16 +974,16 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>1.160214</v>
+        <v>0.03</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.060934</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -996,251 +996,31 @@
         <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>2.436662</v>
+        <v>0.02</v>
       </c>
       <c r="F26" t="n">
-        <v>0.799177</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.042128</v>
+        <v>1.02</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.628712</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ipca_acum_12m</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>44834</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D28" t="n">
-        <v>49</v>
-      </c>
-      <c r="E28" t="n">
-        <v>7.168596</v>
-      </c>
-      <c r="F28" t="n">
-        <v>4.57612</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>igp_m_acum_12m</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="n">
-        <v>44834</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D29" t="n">
-        <v>49</v>
-      </c>
-      <c r="E29" t="n">
-        <v>8.248760000000001</v>
-      </c>
-      <c r="F29" t="n">
-        <v>3.348378</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>inpc_acum_12m</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>44834</v>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D30" t="n">
-        <v>49</v>
-      </c>
-      <c r="E30" t="n">
-        <v>7.191214</v>
-      </c>
-      <c r="F30" t="n">
-        <v>4.293633</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>dif_selic_meta</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>46326</v>
-      </c>
-      <c r="D31" t="n">
-        <v>60</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>dif_selic_over</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>46326</v>
-      </c>
-      <c r="D32" t="n">
-        <v>60</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.004641</v>
-      </c>
-      <c r="F32" t="n">
-        <v>-0.000457</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>dif_cdi</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>46326</v>
-      </c>
-      <c r="D33" t="n">
-        <v>60</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.004641</v>
-      </c>
-      <c r="F33" t="n">
-        <v>-0.000457</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_total</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D34" t="n">
-        <v>58</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D35" t="n">
-        <v>58</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="F37" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,51 +477,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>1.25</v>
+        <v>0.024801</v>
       </c>
       <c r="F3" t="n">
-        <v>0.82</v>
+        <v>0.050788</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.64</v>
+        <v>0.024801</v>
       </c>
       <c r="F4" t="n">
-        <v>1.57</v>
+        <v>0.050788</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,7 +534,7 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="F5" t="n">
         <v>0.82</v>
@@ -543,51 +543,51 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>97.48671</v>
+        <v>0.64</v>
       </c>
       <c r="F6" t="n">
-        <v>109.91611</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>5.6424</v>
+        <v>1.16</v>
       </c>
       <c r="F7" t="n">
-        <v>5.0435</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,16 +600,16 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>4511956</v>
+        <v>97.48845</v>
       </c>
       <c r="F8" t="n">
-        <v>7397669</v>
+        <v>110.40624</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -622,60 +622,60 @@
         <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>2601017</v>
+        <v>96.53555</v>
       </c>
       <c r="F9" t="n">
-        <v>4670170</v>
+        <v>111.71919</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>2.33</v>
+        <v>5.643</v>
       </c>
       <c r="F10" t="n">
-        <v>5.04</v>
+        <v>5.0521</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>1.43</v>
+        <v>5.6424</v>
       </c>
       <c r="F11" t="n">
-        <v>3.35</v>
+        <v>5.0515</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>2.99</v>
+        <v>4511956</v>
       </c>
       <c r="F12" t="n">
-        <v>6.03</v>
+        <v>7397669</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,236 +710,236 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>22.89</v>
+        <v>1910940</v>
       </c>
       <c r="F13" t="n">
-        <v>32.26</v>
+        <v>2727499</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>367927</v>
+        <v>2601017</v>
       </c>
       <c r="F14" t="n">
-        <v>362821</v>
+        <v>4670170</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.608989</v>
+        <v>2.33</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.219358</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4094</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.640774</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D17" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>1.896096</v>
+        <v>22.89</v>
       </c>
       <c r="F17" t="n">
-        <v>0.480339</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>2.436662</v>
+        <v>367927</v>
       </c>
       <c r="F18" t="n">
-        <v>0.799177</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.042128</v>
+        <v>1.60818</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.628712</v>
+        <v>0.340229</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D20" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>7.168596</v>
+        <v>1.362679</v>
       </c>
       <c r="F20" t="n">
-        <v>4.57612</v>
+        <v>-2.420065</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D21" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>8.248760000000001</v>
+        <v>-0.409357</v>
       </c>
       <c r="F21" t="n">
-        <v>3.348378</v>
+        <v>-2.486055</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D22" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>7.191214</v>
+        <v>-0.4094</v>
       </c>
       <c r="F22" t="n">
-        <v>4.293633</v>
+        <v>-2.486342</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1.896096</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03</v>
+        <v>1.160214</v>
       </c>
       <c r="F24" t="n">
-        <v>0.16</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,53 +974,229 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03</v>
+        <v>2.436662</v>
       </c>
       <c r="F25" t="n">
-        <v>0.03</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02</v>
+        <v>-0.042128</v>
       </c>
       <c r="F26" t="n">
-        <v>0.23</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>ipca_acum_12m</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>44834</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D27" t="n">
+        <v>49</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7.168596</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.57612</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>igp_m_acum_12m</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>44834</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D28" t="n">
+        <v>49</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8.248760000000001</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.348378</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>inpc_acum_12m</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>44834</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D29" t="n">
+        <v>49</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7.191214</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.293633</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>dif_selic_meta</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="D30" t="n">
+        <v>60</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>dif_selic_over</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="D31" t="n">
+        <v>60</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.004455</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.000457</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>dif_cdi</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="D32" t="n">
+        <v>60</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.004455</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.000457</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_total</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D33" t="n">
+        <v>58</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D34" t="n">
+        <v>58</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>dif_juros_credito_total</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D27" t="n">
+      <c r="B35" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D35" t="n">
         <v>58</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E35" t="n">
         <v>1.02</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F35" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -477,7 +477,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -499,29 +499,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>0.024801</v>
+        <v>1.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.050788</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,16 +534,16 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="F5" t="n">
-        <v>0.82</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -556,38 +556,38 @@
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F6" t="n">
-        <v>1.57</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>1.16</v>
+        <v>97.48845</v>
       </c>
       <c r="F7" t="n">
-        <v>0.82</v>
+        <v>110.40624</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>97.48845</v>
+        <v>96.53555</v>
       </c>
       <c r="F8" t="n">
-        <v>110.40624</v>
+        <v>111.71919</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>96.53555</v>
+        <v>5.643</v>
       </c>
       <c r="F9" t="n">
-        <v>111.71919</v>
+        <v>5.0826</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.643</v>
+        <v>5.6424</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0521</v>
+        <v>5.082</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0515</v>
+        <v>7397669</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="F12" t="n">
-        <v>7397669</v>
+        <v>2727499</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="F13" t="n">
-        <v>2727499</v>
+        <v>4670170</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="F14" t="n">
-        <v>4670170</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>5.04</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,10 +776,10 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="F16" t="n">
-        <v>3.35</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="17">
@@ -889,7 +889,7 @@
         <v>-0.409357</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.486055</v>
+        <v>-1.897354</v>
       </c>
     </row>
     <row r="22">
@@ -911,7 +911,7 @@
         <v>-0.4094</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.486342</v>
+        <v>-1.897573</v>
       </c>
     </row>
     <row r="23">
@@ -1093,7 +1093,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1115,29 +1115,29 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.004455</v>
+        <v>0.03</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000457</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1153,13 +1153,13 @@
         <v>0.03</v>
       </c>
       <c r="F33" t="n">
-        <v>0.16</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,10 +1172,10 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F34" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="35">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -477,7 +477,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.024801</v>
+        <v>0.024925</v>
       </c>
       <c r="F3" t="n">
         <v>0.050788</v>
@@ -499,29 +499,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>1.25</v>
+        <v>0.024925</v>
       </c>
       <c r="F4" t="n">
-        <v>0.82</v>
+        <v>0.050788</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,16 +534,16 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>0.64</v>
+        <v>1.25</v>
       </c>
       <c r="F5" t="n">
-        <v>1.57</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -556,38 +556,38 @@
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>1.16</v>
+        <v>0.64</v>
       </c>
       <c r="F6" t="n">
-        <v>0.82</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>97.48845</v>
+        <v>1.16</v>
       </c>
       <c r="F7" t="n">
-        <v>110.40624</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>96.53555</v>
+        <v>97.48845</v>
       </c>
       <c r="F8" t="n">
-        <v>111.71919</v>
+        <v>110.40624</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>5.643</v>
+        <v>96.53555</v>
       </c>
       <c r="F9" t="n">
-        <v>5.0826</v>
+        <v>111.71919</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.6424</v>
+        <v>5.643</v>
       </c>
       <c r="F10" t="n">
-        <v>5.082</v>
+        <v>5.0564</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4511956</v>
+        <v>5.6424</v>
       </c>
       <c r="F11" t="n">
-        <v>7397669</v>
+        <v>5.0558</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1910940</v>
+        <v>4511956</v>
       </c>
       <c r="F12" t="n">
-        <v>2727499</v>
+        <v>7397669</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2601017</v>
+        <v>1910940</v>
       </c>
       <c r="F13" t="n">
-        <v>4670170</v>
+        <v>2727499</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.33</v>
+        <v>2601017</v>
       </c>
       <c r="F14" t="n">
-        <v>5.04</v>
+        <v>4670170</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="F15" t="n">
-        <v>3.35</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>2.99</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>6.03</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,10 +798,10 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>22.89</v>
+        <v>2.99</v>
       </c>
       <c r="F17" t="n">
-        <v>32.26</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="18">
@@ -889,7 +889,7 @@
         <v>-0.409357</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.897354</v>
+        <v>-2.403057</v>
       </c>
     </row>
     <row r="22">
@@ -911,7 +911,7 @@
         <v>-0.4094</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.897573</v>
+        <v>-2.403336</v>
       </c>
     </row>
     <row r="23">
@@ -1093,7 +1093,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,7 +1106,7 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004455</v>
+        <v>0.004331</v>
       </c>
       <c r="F31" t="n">
         <v>-0.000457</v>
@@ -1115,29 +1115,29 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.03</v>
+        <v>0.004331</v>
       </c>
       <c r="F32" t="n">
-        <v>0.16</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1153,13 +1153,13 @@
         <v>0.03</v>
       </c>
       <c r="F33" t="n">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F34" t="n">
-        <v>0.23</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,10 +1194,10 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>1.02</v>
+        <v>0.02</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.024925</v>
+        <v>0.025079</v>
       </c>
       <c r="F3" t="n">
         <v>0.050788</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.024925</v>
+        <v>0.025079</v>
       </c>
       <c r="F4" t="n">
         <v>0.050788</v>
@@ -741,7 +741,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>5.04</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="F16" t="n">
-        <v>3.35</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,10 +798,10 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="F17" t="n">
-        <v>6.03</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="18">
@@ -1106,7 +1106,7 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004331</v>
+        <v>0.004177</v>
       </c>
       <c r="F31" t="n">
         <v>-0.000457</v>
@@ -1128,7 +1128,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.004331</v>
+        <v>0.004177</v>
       </c>
       <c r="F32" t="n">
         <v>-0.000457</v>
@@ -1137,7 +1137,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1153,13 +1153,13 @@
         <v>0.03</v>
       </c>
       <c r="F33" t="n">
-        <v>0.16</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F34" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,10 +1194,10 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>0.02</v>
+        <v>1.02</v>
       </c>
       <c r="F35" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.025079</v>
+        <v>0.025278</v>
       </c>
       <c r="F3" t="n">
         <v>0.050788</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.025079</v>
+        <v>0.025278</v>
       </c>
       <c r="F4" t="n">
         <v>0.050788</v>
@@ -647,7 +647,7 @@
         <v>5.643</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0564</v>
+        <v>5.014</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.6424</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0558</v>
+        <v>5.0134</v>
       </c>
     </row>
     <row r="12">
@@ -741,7 +741,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="F15" t="n">
-        <v>3.35</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>2.99</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>6.03</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>22.89</v>
+        <v>2.99</v>
       </c>
       <c r="F17" t="n">
-        <v>32.26</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>367927</v>
+        <v>22.89</v>
       </c>
       <c r="F18" t="n">
-        <v>362821</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>1.60818</v>
+        <v>367927</v>
       </c>
       <c r="F19" t="n">
-        <v>0.340229</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>1.362679</v>
+        <v>1.60818</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.420065</v>
+        <v>0.340229</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.409357</v>
+        <v>1.362679</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.403057</v>
+        <v>-2.420065</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4094</v>
+        <v>-0.409357</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.403336</v>
+        <v>-3.221448</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.896096</v>
+        <v>-0.4094</v>
       </c>
       <c r="F23" t="n">
-        <v>0.480339</v>
+        <v>-3.221821</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.160214</v>
+        <v>1.896096</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.060934</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.436662</v>
+        <v>1.160214</v>
       </c>
       <c r="F25" t="n">
-        <v>0.799177</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.042128</v>
+        <v>2.436662</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.628712</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>7.168596</v>
+        <v>-0.042128</v>
       </c>
       <c r="F27" t="n">
-        <v>4.57612</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,16 +1040,16 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.248760000000001</v>
+        <v>7.168596</v>
       </c>
       <c r="F28" t="n">
-        <v>3.348378</v>
+        <v>4.57612</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,38 +1062,38 @@
         <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>7.191214</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>4.293633</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>7.191214</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>4.293633</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,16 +1106,16 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004177</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1128,7 +1128,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.004177</v>
+        <v>0.003978</v>
       </c>
       <c r="F32" t="n">
         <v>-0.000457</v>
@@ -1137,29 +1137,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03</v>
+        <v>0.003978</v>
       </c>
       <c r="F33" t="n">
-        <v>0.03</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F34" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>1.02</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.025278</v>
+        <v>0.025543</v>
       </c>
       <c r="F3" t="n">
         <v>0.050788</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.025278</v>
+        <v>0.025543</v>
       </c>
       <c r="F4" t="n">
         <v>0.050788</v>
@@ -647,7 +647,7 @@
         <v>5.643</v>
       </c>
       <c r="F10" t="n">
-        <v>5.014</v>
+        <v>5.0277</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.6424</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0134</v>
+        <v>5.027</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>-0.409357</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.221448</v>
+        <v>-2.957015</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>-0.4094</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.221821</v>
+        <v>-2.959288</v>
       </c>
     </row>
     <row r="24">
@@ -1128,7 +1128,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003978</v>
+        <v>0.003713</v>
       </c>
       <c r="F32" t="n">
         <v>-0.000457</v>
@@ -1150,7 +1150,7 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003978</v>
+        <v>0.003713</v>
       </c>
       <c r="F33" t="n">
         <v>-0.000457</v>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.025543</v>
+        <v>0.025915</v>
       </c>
       <c r="F3" t="n">
         <v>0.050788</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.025543</v>
+        <v>0.025915</v>
       </c>
       <c r="F4" t="n">
         <v>0.050788</v>
@@ -647,7 +647,7 @@
         <v>5.643</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0277</v>
+        <v>5.0383</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.6424</v>
       </c>
       <c r="F11" t="n">
-        <v>5.027</v>
+        <v>5.0377</v>
       </c>
     </row>
     <row r="12">
@@ -807,51 +807,51 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="F18" t="n">
-        <v>32.26</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>367927</v>
+        <v>1.60818</v>
       </c>
       <c r="F19" t="n">
-        <v>362821</v>
+        <v>0.340229</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>1.60818</v>
+        <v>1.362679</v>
       </c>
       <c r="F20" t="n">
-        <v>0.340229</v>
+        <v>-2.420065</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>1.362679</v>
+        <v>-0.409357</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.420065</v>
+        <v>-2.752418</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.409357</v>
+        <v>-0.4094</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.957015</v>
+        <v>-2.752736</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4094</v>
+        <v>1.896096</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.959288</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.896096</v>
+        <v>1.160214</v>
       </c>
       <c r="F24" t="n">
-        <v>0.480339</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>1.160214</v>
+        <v>2.436662</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.060934</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2.436662</v>
+        <v>-0.042128</v>
       </c>
       <c r="F26" t="n">
-        <v>0.799177</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.042128</v>
+        <v>7.168596</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.628712</v>
+        <v>4.57612</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,16 +1040,16 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>7.168596</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>4.57612</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,38 +1062,38 @@
         <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>8.248760000000001</v>
+        <v>7.191214</v>
       </c>
       <c r="F29" t="n">
-        <v>3.348378</v>
+        <v>4.293633</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>7.191214</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>4.293633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,16 +1106,16 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.003341</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1128,7 +1128,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003713</v>
+        <v>0.003341</v>
       </c>
       <c r="F32" t="n">
         <v>-0.000457</v>
@@ -1137,29 +1137,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003713</v>
+        <v>0.03</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000457</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1175,13 +1175,13 @@
         <v>0.03</v>
       </c>
       <c r="F34" t="n">
-        <v>0.16</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,54 +1194,10 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F35" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F36" t="n">
         <v>0.23</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,7 +647,7 @@
         <v>5.643</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0383</v>
+        <v>5.0377</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.6424</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0377</v>
+        <v>5.0371</v>
       </c>
     </row>
     <row r="12">
@@ -807,51 +807,51 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>367927</v>
+        <v>22.89</v>
       </c>
       <c r="F18" t="n">
-        <v>362821</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>1.60818</v>
+        <v>367927</v>
       </c>
       <c r="F19" t="n">
-        <v>0.340229</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>1.362679</v>
+        <v>1.60818</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.420065</v>
+        <v>0.340229</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.409357</v>
+        <v>1.362679</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.752418</v>
+        <v>-2.420065</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4094</v>
+        <v>-0.409357</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.752736</v>
+        <v>-2.763999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.896096</v>
+        <v>-0.4094</v>
       </c>
       <c r="F23" t="n">
-        <v>0.480339</v>
+        <v>-2.764319</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.160214</v>
+        <v>1.896096</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.060934</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.436662</v>
+        <v>1.160214</v>
       </c>
       <c r="F25" t="n">
-        <v>0.799177</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.042128</v>
+        <v>2.436662</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.628712</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>7.168596</v>
+        <v>-0.042128</v>
       </c>
       <c r="F27" t="n">
-        <v>4.57612</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,16 +1040,16 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.248760000000001</v>
+        <v>7.168596</v>
       </c>
       <c r="F28" t="n">
-        <v>3.348378</v>
+        <v>4.57612</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,38 +1062,38 @@
         <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>7.191214</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>4.293633</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>7.191214</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>4.293633</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,16 +1106,16 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003341</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1137,29 +1137,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03</v>
+        <v>0.003341</v>
       </c>
       <c r="F33" t="n">
-        <v>0.16</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1175,13 +1175,13 @@
         <v>0.03</v>
       </c>
       <c r="F34" t="n">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,10 +1194,54 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
         <v>0.02</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F36" t="n">
         <v>0.23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.025915</v>
+        <v>0.026472</v>
       </c>
       <c r="F3" t="n">
         <v>0.050788</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.025915</v>
+        <v>0.026472</v>
       </c>
       <c r="F4" t="n">
         <v>0.050788</v>
@@ -807,51 +807,51 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="F18" t="n">
-        <v>32.26</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>367927</v>
+        <v>1.60818</v>
       </c>
       <c r="F19" t="n">
-        <v>362821</v>
+        <v>0.340229</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>1.60818</v>
+        <v>1.362679</v>
       </c>
       <c r="F20" t="n">
-        <v>0.340229</v>
+        <v>-2.420065</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>1.362679</v>
+        <v>-0.409357</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.420065</v>
+        <v>-2.763999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.409357</v>
+        <v>-0.4094</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.763999</v>
+        <v>-2.764319</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4094</v>
+        <v>1.896096</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.764319</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.896096</v>
+        <v>1.160214</v>
       </c>
       <c r="F24" t="n">
-        <v>0.480339</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>1.160214</v>
+        <v>2.436662</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.060934</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2.436662</v>
+        <v>-0.042128</v>
       </c>
       <c r="F26" t="n">
-        <v>0.799177</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.042128</v>
+        <v>7.168596</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.628712</v>
+        <v>4.57612</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,16 +1040,16 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>7.168596</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>4.57612</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,38 +1062,38 @@
         <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>8.248760000000001</v>
+        <v>7.191214</v>
       </c>
       <c r="F29" t="n">
-        <v>3.348378</v>
+        <v>4.293633</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>7.191214</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>4.293633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,16 +1106,16 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.002784</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1128,7 +1128,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003341</v>
+        <v>0.002784</v>
       </c>
       <c r="F32" t="n">
         <v>-0.000457</v>
@@ -1137,29 +1137,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003341</v>
+        <v>0.03</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000457</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1175,13 +1175,13 @@
         <v>0.03</v>
       </c>
       <c r="F34" t="n">
-        <v>0.16</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,54 +1194,10 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F35" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F36" t="n">
         <v>0.23</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.026472</v>
+        <v>0.0274</v>
       </c>
       <c r="F3" t="n">
         <v>0.050788</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.026472</v>
+        <v>0.0274</v>
       </c>
       <c r="F4" t="n">
         <v>0.050788</v>
@@ -647,7 +647,7 @@
         <v>5.643</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0377</v>
+        <v>5.5007</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.6424</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0371</v>
+        <v>5.4998</v>
       </c>
     </row>
     <row r="12">
@@ -807,51 +807,51 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>367927</v>
+        <v>22.89</v>
       </c>
       <c r="F18" t="n">
-        <v>362821</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>1.60818</v>
+        <v>367927</v>
       </c>
       <c r="F19" t="n">
-        <v>0.340229</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>1.362679</v>
+        <v>1.60818</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.420065</v>
+        <v>0.340229</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.409357</v>
+        <v>1.362679</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.763999</v>
+        <v>-2.420065</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4094</v>
+        <v>-0.409357</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.764319</v>
+        <v>6.172673</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.896096</v>
+        <v>-0.4094</v>
       </c>
       <c r="F23" t="n">
-        <v>0.480339</v>
+        <v>6.167596</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.160214</v>
+        <v>1.896096</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.060934</v>
+        <v>0.480339</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.436662</v>
+        <v>1.160214</v>
       </c>
       <c r="F25" t="n">
-        <v>0.799177</v>
+        <v>-0.060934</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.042128</v>
+        <v>2.436662</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.628712</v>
+        <v>0.799177</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>7.168596</v>
+        <v>-0.042128</v>
       </c>
       <c r="F27" t="n">
-        <v>4.57612</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,16 +1040,16 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.248760000000001</v>
+        <v>7.168596</v>
       </c>
       <c r="F28" t="n">
-        <v>3.348378</v>
+        <v>4.57612</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,38 +1062,38 @@
         <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>7.191214</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>4.293633</v>
+        <v>3.348378</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>7.191214</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>4.293633</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,16 +1106,16 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.002784</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1128,7 +1128,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.002784</v>
+        <v>0.001856</v>
       </c>
       <c r="F32" t="n">
         <v>-0.000457</v>
@@ -1137,29 +1137,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03</v>
+        <v>0.001856</v>
       </c>
       <c r="F33" t="n">
-        <v>0.16</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1175,13 +1175,13 @@
         <v>0.03</v>
       </c>
       <c r="F34" t="n">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,10 +1194,54 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
         <v>0.02</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F36" t="n">
         <v>0.23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0274</v>
+        <v>0.029256</v>
       </c>
       <c r="F3" t="n">
         <v>0.050788</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0274</v>
+        <v>0.029256</v>
       </c>
       <c r="F4" t="n">
         <v>0.050788</v>
@@ -647,7 +647,7 @@
         <v>5.643</v>
       </c>
       <c r="F10" t="n">
-        <v>5.5007</v>
+        <v>5.342</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.6424</v>
       </c>
       <c r="F11" t="n">
-        <v>5.4998</v>
+        <v>5.3414</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>-0.409357</v>
       </c>
       <c r="F22" t="n">
-        <v>6.172673</v>
+        <v>3.109498</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>-0.4094</v>
       </c>
       <c r="F23" t="n">
-        <v>6.167596</v>
+        <v>3.109859</v>
       </c>
     </row>
     <row r="24">
@@ -1128,7 +1128,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001856</v>
+        <v>-0</v>
       </c>
       <c r="F32" t="n">
         <v>-0.000457</v>
@@ -1150,7 +1150,7 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001856</v>
+        <v>-0</v>
       </c>
       <c r="F33" t="n">
         <v>-0.000457</v>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,16 +550,16 @@
         <v>44500</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
         <v>0.64</v>
       </c>
       <c r="F6" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="7">
@@ -647,7 +647,7 @@
         <v>5.643</v>
       </c>
       <c r="F10" t="n">
-        <v>5.342</v>
+        <v>5.3744</v>
       </c>
     </row>
     <row r="11">
@@ -669,189 +669,189 @@
         <v>5.6424</v>
       </c>
       <c r="F11" t="n">
-        <v>5.3414</v>
+        <v>5.3738</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="F12" t="n">
-        <v>7397669</v>
+        <v>2759442</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="F13" t="n">
-        <v>2727499</v>
+        <v>4684766</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="F14" t="n">
-        <v>4670170</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>5.04</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="F16" t="n">
-        <v>3.35</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="F17" t="n">
-        <v>6.03</v>
+        <v>32.36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="F18" t="n">
-        <v>32.26</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>367927</v>
+        <v>1.60818</v>
       </c>
       <c r="F19" t="n">
-        <v>362821</v>
+        <v>0.340229</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>1.60818</v>
+        <v>1.362679</v>
       </c>
       <c r="F20" t="n">
-        <v>0.340229</v>
+        <v>-2.420065</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>1.362679</v>
+        <v>-0.409357</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.420065</v>
+        <v>3.734872</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,126 +908,126 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.409357</v>
+        <v>-0.4094</v>
       </c>
       <c r="F22" t="n">
-        <v>3.109498</v>
+        <v>3.735305</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4094</v>
+        <v>1.160214</v>
       </c>
       <c r="F23" t="n">
-        <v>3.109859</v>
+        <v>1.008791</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>1.896096</v>
+        <v>2.436662</v>
       </c>
       <c r="F24" t="n">
-        <v>0.480339</v>
+        <v>0.091615</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>1.160214</v>
+        <v>-0.042128</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.060934</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E26" t="n">
-        <v>2.436662</v>
+        <v>7.168596</v>
       </c>
       <c r="F26" t="n">
-        <v>0.799177</v>
+        <v>4.57612</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.042128</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.628712</v>
+        <v>5.246487</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>7.168596</v>
+        <v>7.191214</v>
       </c>
       <c r="F28" t="n">
-        <v>4.57612</v>
+        <v>4.293633</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>8.248760000000001</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>3.348378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>7.191214</v>
+        <v>-0</v>
       </c>
       <c r="F30" t="n">
-        <v>4.293633</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,142 +1106,98 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E32" t="n">
-        <v>-0</v>
+        <v>0.03</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000457</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>-0</v>
+        <v>0.03</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000457</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D34" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E34" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F34" t="n">
-        <v>0.16</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>0.03</v>
+        <v>1.02</v>
       </c>
       <c r="F35" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
         <v>0.029256</v>
@@ -503,13 +503,13 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
         <v>0.029256</v>
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
-        <v>5.643</v>
+        <v>5.6199</v>
       </c>
       <c r="F10" t="n">
-        <v>5.3744</v>
+        <v>5.4212</v>
       </c>
     </row>
     <row r="11">
@@ -657,25 +657,25 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>5.6424</v>
+        <v>5.6193</v>
       </c>
       <c r="F11" t="n">
-        <v>5.3738</v>
+        <v>5.4206</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>60</v>
       </c>
       <c r="E12" t="n">
-        <v>1910940</v>
+        <v>4511956</v>
       </c>
       <c r="F12" t="n">
-        <v>2759442</v>
+        <v>7444208</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>2601017</v>
+        <v>1910940</v>
       </c>
       <c r="F13" t="n">
-        <v>4684766</v>
+        <v>2759442</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>2.33</v>
+        <v>2601017</v>
       </c>
       <c r="F14" t="n">
-        <v>4.98</v>
+        <v>4684766</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="F15" t="n">
-        <v>3.28</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>2.99</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>5.99</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,16 +798,16 @@
         <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>22.89</v>
+        <v>2.99</v>
       </c>
       <c r="F17" t="n">
-        <v>32.36</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -820,38 +820,38 @@
         <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>367927</v>
+        <v>22.89</v>
       </c>
       <c r="F18" t="n">
-        <v>362821</v>
+        <v>32.36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>1.60818</v>
+        <v>367927</v>
       </c>
       <c r="F19" t="n">
-        <v>0.340229</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,82 +864,82 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>1.362679</v>
+        <v>1.60818</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.420065</v>
+        <v>0.340229</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.409357</v>
+        <v>1.362679</v>
       </c>
       <c r="F21" t="n">
-        <v>3.734872</v>
+        <v>-2.420065</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4094</v>
+        <v>-0.70108</v>
       </c>
       <c r="F22" t="n">
-        <v>3.735305</v>
+        <v>4.63819</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D23" t="n">
         <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>1.160214</v>
+        <v>-0.701155</v>
       </c>
       <c r="F23" t="n">
-        <v>1.008791</v>
+        <v>4.638727</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>2.436662</v>
+        <v>1.896096</v>
       </c>
       <c r="F24" t="n">
-        <v>0.091615</v>
+        <v>0.429647</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.042128</v>
+        <v>1.160214</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.628712</v>
+        <v>1.008791</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D26" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>7.168596</v>
+        <v>2.436662</v>
       </c>
       <c r="F26" t="n">
-        <v>4.57612</v>
+        <v>0.091615</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D27" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>8.248760000000001</v>
+        <v>-0.042128</v>
       </c>
       <c r="F27" t="n">
-        <v>5.246487</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>7.191214</v>
+        <v>7.168596</v>
       </c>
       <c r="F28" t="n">
-        <v>4.293633</v>
+        <v>4.57612</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>5.246487</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>-0</v>
+        <v>7.191214</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000457</v>
+        <v>4.293633</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D32" t="n">
         <v>59</v>
       </c>
       <c r="E32" t="n">
-        <v>0.03</v>
+        <v>0.00406</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D33" t="n">
         <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03</v>
+        <v>0.00406</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.08</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,31 +1172,75 @@
         <v>59</v>
       </c>
       <c r="E34" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D35" t="n">
+        <v>59</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D36" t="n">
+        <v>59</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>dif_juros_credito_total</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D35" t="n">
-        <v>59</v>
-      </c>
-      <c r="E35" t="n">
+      <c r="B37" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D37" t="n">
+        <v>59</v>
+      </c>
+      <c r="E37" t="n">
         <v>1.02</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>0.13</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,95 +499,95 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D4" t="n">
         <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>0.029256</v>
+        <v>1.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.050788</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E5" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="F5" t="n">
-        <v>0.82</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F6" t="n">
-        <v>1.47</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>1.16</v>
+        <v>97.48845</v>
       </c>
       <c r="F7" t="n">
-        <v>0.82</v>
+        <v>110.40624</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>97.48845</v>
+        <v>96.53555</v>
       </c>
       <c r="F8" t="n">
-        <v>110.40624</v>
+        <v>111.71919</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
-        <v>96.53555</v>
+        <v>5.6199</v>
       </c>
       <c r="F9" t="n">
-        <v>111.71919</v>
+        <v>5.4212</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>60</v>
       </c>
       <c r="E10" t="n">
-        <v>5.6199</v>
+        <v>5.6193</v>
       </c>
       <c r="F10" t="n">
-        <v>5.4212</v>
+        <v>5.4206</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D11" t="n">
         <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>5.6193</v>
+        <v>4511956</v>
       </c>
       <c r="F11" t="n">
-        <v>5.4206</v>
+        <v>7444208</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>60</v>
       </c>
       <c r="E12" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="F12" t="n">
-        <v>7444208</v>
+        <v>2759442</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="F13" t="n">
-        <v>2759442</v>
+        <v>4684766</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="F14" t="n">
-        <v>4684766</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>4.98</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="F16" t="n">
-        <v>3.28</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,16 +798,16 @@
         <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="F17" t="n">
-        <v>5.99</v>
+        <v>32.36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -820,38 +820,38 @@
         <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="F18" t="n">
-        <v>32.36</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>367927</v>
+        <v>1.60818</v>
       </c>
       <c r="F19" t="n">
-        <v>362821</v>
+        <v>0.340229</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>1.60818</v>
+        <v>1.362679</v>
       </c>
       <c r="F20" t="n">
-        <v>0.340229</v>
+        <v>-2.420065</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E21" t="n">
-        <v>1.362679</v>
+        <v>-0.70108</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.420065</v>
+        <v>4.63819</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>59</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.70108</v>
+        <v>-0.701155</v>
       </c>
       <c r="F22" t="n">
-        <v>4.63819</v>
+        <v>4.638727</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D23" t="n">
         <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.701155</v>
+        <v>1.896096</v>
       </c>
       <c r="F23" t="n">
-        <v>4.638727</v>
+        <v>0.429647</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>1.896096</v>
+        <v>1.160214</v>
       </c>
       <c r="F24" t="n">
-        <v>0.429647</v>
+        <v>1.008791</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,16 +974,16 @@
         <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>1.160214</v>
+        <v>2.436662</v>
       </c>
       <c r="F25" t="n">
-        <v>1.008791</v>
+        <v>0.091615</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -996,170 +996,170 @@
         <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2.436662</v>
+        <v>-0.042128</v>
       </c>
       <c r="F26" t="n">
-        <v>0.091615</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.042128</v>
+        <v>7.168596</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.628712</v>
+        <v>4.57612</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E28" t="n">
-        <v>7.168596</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>4.57612</v>
+        <v>5.246487</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>8.248760000000001</v>
+        <v>7.191214</v>
       </c>
       <c r="F29" t="n">
-        <v>5.246487</v>
+        <v>4.293633</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>7.191214</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>4.293633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.00406</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
         <v>59</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00406</v>
+        <v>0.03</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000457</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D33" t="n">
         <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>0.00406</v>
+        <v>0.03</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000457</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>59</v>
       </c>
       <c r="E34" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>0.03</v>
+        <v>1.02</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D36" t="n">
-        <v>59</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D37" t="n">
-        <v>59</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="F37" t="n">
         <v>0.13</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,95 +499,95 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D4" t="n">
         <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>1.25</v>
+        <v>0.029256</v>
       </c>
       <c r="F4" t="n">
-        <v>0.82</v>
+        <v>0.050788</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>0.64</v>
+        <v>1.25</v>
       </c>
       <c r="F5" t="n">
-        <v>1.47</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
-        <v>1.16</v>
+        <v>0.64</v>
       </c>
       <c r="F6" t="n">
-        <v>0.82</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>97.48845</v>
+        <v>1.16</v>
       </c>
       <c r="F7" t="n">
-        <v>110.40624</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>96.53555</v>
+        <v>97.48845</v>
       </c>
       <c r="F8" t="n">
-        <v>111.71919</v>
+        <v>110.40624</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D9" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>5.6199</v>
+        <v>96.53555</v>
       </c>
       <c r="F9" t="n">
-        <v>5.4212</v>
+        <v>111.71919</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>60</v>
       </c>
       <c r="E10" t="n">
-        <v>5.6193</v>
+        <v>5.6199</v>
       </c>
       <c r="F10" t="n">
-        <v>5.4206</v>
+        <v>5.4212</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D11" t="n">
         <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>4511956</v>
+        <v>5.6193</v>
       </c>
       <c r="F11" t="n">
-        <v>7444208</v>
+        <v>5.4206</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>60</v>
       </c>
       <c r="E12" t="n">
-        <v>1910940</v>
+        <v>4511956</v>
       </c>
       <c r="F12" t="n">
-        <v>2759442</v>
+        <v>7444208</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>2601017</v>
+        <v>1910940</v>
       </c>
       <c r="F13" t="n">
-        <v>4684766</v>
+        <v>2759442</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>2.33</v>
+        <v>2601017</v>
       </c>
       <c r="F14" t="n">
-        <v>4.98</v>
+        <v>4684766</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="F15" t="n">
-        <v>3.28</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>2.99</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>5.99</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,16 +798,16 @@
         <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>22.89</v>
+        <v>2.99</v>
       </c>
       <c r="F17" t="n">
-        <v>32.36</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -820,38 +820,38 @@
         <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>367927</v>
+        <v>22.89</v>
       </c>
       <c r="F18" t="n">
-        <v>362821</v>
+        <v>32.36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>1.60818</v>
+        <v>367927</v>
       </c>
       <c r="F19" t="n">
-        <v>0.340229</v>
+        <v>362821</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>1.362679</v>
+        <v>1.60818</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.420065</v>
+        <v>0.340229</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="D21" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.70108</v>
+        <v>1.362679</v>
       </c>
       <c r="F21" t="n">
-        <v>4.63819</v>
+        <v>-2.420065</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>59</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.701155</v>
+        <v>-0.70108</v>
       </c>
       <c r="F22" t="n">
-        <v>4.638727</v>
+        <v>4.63819</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D23" t="n">
         <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>1.896096</v>
+        <v>-0.701155</v>
       </c>
       <c r="F23" t="n">
-        <v>0.429647</v>
+        <v>4.638727</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>1.160214</v>
+        <v>1.896096</v>
       </c>
       <c r="F24" t="n">
-        <v>1.008791</v>
+        <v>0.429647</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,16 +974,16 @@
         <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>2.436662</v>
+        <v>1.160214</v>
       </c>
       <c r="F25" t="n">
-        <v>0.091615</v>
+        <v>1.008791</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -996,170 +996,170 @@
         <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.042128</v>
+        <v>2.436662</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.628712</v>
+        <v>0.091615</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44834</v>
+        <v>44530</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>7.168596</v>
+        <v>-0.042128</v>
       </c>
       <c r="F27" t="n">
-        <v>4.57612</v>
+        <v>-2.628712</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.248760000000001</v>
+        <v>7.168596</v>
       </c>
       <c r="F28" t="n">
-        <v>5.246487</v>
+        <v>4.57612</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E29" t="n">
-        <v>7.191214</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>4.293633</v>
+        <v>5.246487</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44530</v>
+        <v>44834</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>7.191214</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>4.293633</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D31" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.00406</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D32" t="n">
         <v>59</v>
       </c>
       <c r="E32" t="n">
-        <v>0.03</v>
+        <v>0.00406</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D33" t="n">
         <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03</v>
+        <v>0.00406</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.08</v>
+        <v>-0.000457</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,31 +1172,75 @@
         <v>59</v>
       </c>
       <c r="E34" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D35" t="n">
+        <v>59</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D36" t="n">
+        <v>59</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>dif_juros_credito_total</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D35" t="n">
-        <v>59</v>
-      </c>
-      <c r="E35" t="n">
+      <c r="B37" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D37" t="n">
+        <v>59</v>
+      </c>
+      <c r="E37" t="n">
         <v>1.02</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>0.13</v>
       </c>
     </row>
